--- a/nr-add-mapping/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-dr-organization.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$233</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$224</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7538" uniqueCount="753">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7248" uniqueCount="737">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-05T10:02:39+00:00</t>
+    <t>2024-03-19T08:59:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2070,55 +2070,6 @@
   </si>
   <si>
     <t>Les BALs MSS de type ORG ou APP rattachées à une personne morale responsable de l’accès et de l’usage de la BAL (boiteLettreMSS).</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.id</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:emailType</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata</t>
-  </si>
-  <si>
-    <t>as-mailbox-mss-metadata</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata}
-</t>
-  </si>
-  <si>
-    <t>Les attributs 'responsible' et 'phone' ne sont pas disponibles en accès libre.</t>
-  </si>
-  <si>
-    <t>Extension contenant les métadonnées de la mailbox mss.</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.system</t>
-  </si>
-  <si>
-    <t>email</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.value</t>
-  </si>
-  <si>
-    <t>Boîte Aux Lettres (BAL) MSS</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.use</t>
-  </si>
-  <si>
-    <t>Applications can assume that a contact is current unless it explicitly says that it is temporary or old.</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.rank</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.period</t>
   </si>
   <si>
     <t>Organization.address</t>
@@ -2678,7 +2629,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ233"/>
+  <dimension ref="A1:AJ224"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="80.17578125" customWidth="true" bestFit="true"/>
@@ -23911,7 +23862,7 @@
         <v>661</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>620</v>
+        <v>661</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -23922,10 +23873,10 @@
         <v>74</v>
       </c>
       <c r="G208" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H208" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I208" t="s" s="2">
         <v>73</v>
@@ -23934,16 +23885,20 @@
         <v>73</v>
       </c>
       <c r="K208" t="s" s="2">
-        <v>96</v>
+        <v>662</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>97</v>
+        <v>663</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="N208" s="2"/>
-      <c r="O208" s="2"/>
+        <v>664</v>
+      </c>
+      <c r="N208" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="O208" t="s" s="2">
+        <v>666</v>
+      </c>
       <c r="P208" t="s" s="2">
         <v>73</v>
       </c>
@@ -23991,38 +23946,38 @@
         <v>73</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>99</v>
+        <v>661</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH208" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI208" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ208" t="s" s="2">
-        <v>73</v>
+        <v>667</v>
       </c>
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>662</v>
+        <v>668</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>621</v>
+        <v>668</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="E209" s="2"/>
       <c r="F209" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G209" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H209" t="s" s="2">
         <v>73</v>
@@ -24031,21 +23986,23 @@
         <v>73</v>
       </c>
       <c r="J209" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K209" t="s" s="2">
-        <v>102</v>
+        <v>669</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>103</v>
+        <v>670</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>104</v>
+        <v>671</v>
       </c>
       <c r="N209" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="O209" s="2"/>
+        <v>672</v>
+      </c>
+      <c r="O209" t="s" s="2">
+        <v>673</v>
+      </c>
       <c r="P209" t="s" s="2">
         <v>73</v>
       </c>
@@ -24081,45 +24038,43 @@
         <v>73</v>
       </c>
       <c r="AB209" t="s" s="2">
-        <v>106</v>
+        <v>73</v>
       </c>
       <c r="AC209" t="s" s="2">
-        <v>107</v>
+        <v>73</v>
       </c>
       <c r="AD209" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE209" t="s" s="2">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>109</v>
+        <v>668</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH209" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI209" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ209" t="s" s="2">
-        <v>110</v>
+        <v>323</v>
       </c>
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>663</v>
+        <v>674</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="C210" t="s" s="2">
-        <v>623</v>
-      </c>
+        <v>674</v>
+      </c>
+      <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="E210" s="2"/>
       <c r="F210" t="s" s="2">
@@ -24138,17 +24093,15 @@
         <v>73</v>
       </c>
       <c r="K210" t="s" s="2">
-        <v>624</v>
+        <v>96</v>
       </c>
       <c r="L210" t="s" s="2">
-        <v>625</v>
+        <v>97</v>
       </c>
       <c r="M210" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N210" t="s" s="2">
-        <v>105</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="N210" s="2"/>
       <c r="O210" s="2"/>
       <c r="P210" t="s" s="2">
         <v>73</v>
@@ -24197,43 +24150,41 @@
         <v>73</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH210" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI210" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AJ210" t="s" s="2">
-        <v>110</v>
+        <v>73</v>
       </c>
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>664</v>
+        <v>675</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="C211" t="s" s="2">
-        <v>665</v>
-      </c>
+        <v>675</v>
+      </c>
+      <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="E211" s="2"/>
       <c r="F211" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G211" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H211" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I211" t="s" s="2">
         <v>73</v>
@@ -24242,15 +24193,17 @@
         <v>73</v>
       </c>
       <c r="K211" t="s" s="2">
-        <v>666</v>
+        <v>102</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>667</v>
+        <v>103</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>668</v>
-      </c>
-      <c r="N211" s="2"/>
+        <v>104</v>
+      </c>
+      <c r="N211" t="s" s="2">
+        <v>105</v>
+      </c>
       <c r="O211" s="2"/>
       <c r="P211" t="s" s="2">
         <v>73</v>
@@ -24287,16 +24240,16 @@
         <v>73</v>
       </c>
       <c r="AB211" t="s" s="2">
-        <v>73</v>
+        <v>106</v>
       </c>
       <c r="AC211" t="s" s="2">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="AD211" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE211" t="s" s="2">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="AF211" t="s" s="2">
         <v>109</v>
@@ -24316,10 +24269,10 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>669</v>
+        <v>676</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>626</v>
+        <v>676</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -24327,7 +24280,7 @@
       </c>
       <c r="E212" s="2"/>
       <c r="F212" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="G212" t="s" s="2">
         <v>81</v>
@@ -24342,16 +24295,16 @@
         <v>82</v>
       </c>
       <c r="K212" t="s" s="2">
-        <v>162</v>
+        <v>96</v>
       </c>
       <c r="L212" t="s" s="2">
-        <v>627</v>
+        <v>677</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>628</v>
+        <v>678</v>
       </c>
       <c r="N212" t="s" s="2">
-        <v>379</v>
+        <v>679</v>
       </c>
       <c r="O212" s="2"/>
       <c r="P212" t="s" s="2">
@@ -24362,7 +24315,7 @@
         <v>73</v>
       </c>
       <c r="S212" t="s" s="2">
-        <v>670</v>
+        <v>73</v>
       </c>
       <c r="T212" t="s" s="2">
         <v>73</v>
@@ -24377,13 +24330,13 @@
         <v>73</v>
       </c>
       <c r="X212" t="s" s="2">
-        <v>285</v>
+        <v>73</v>
       </c>
       <c r="Y212" t="s" s="2">
-        <v>629</v>
+        <v>73</v>
       </c>
       <c r="Z212" t="s" s="2">
-        <v>630</v>
+        <v>73</v>
       </c>
       <c r="AA212" t="s" s="2">
         <v>73</v>
@@ -24401,7 +24354,7 @@
         <v>73</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>631</v>
+        <v>680</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>74</v>
@@ -24410,7 +24363,7 @@
         <v>81</v>
       </c>
       <c r="AI212" t="s" s="2">
-        <v>632</v>
+        <v>681</v>
       </c>
       <c r="AJ212" t="s" s="2">
         <v>94</v>
@@ -24418,10 +24371,10 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>671</v>
+        <v>682</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>633</v>
+        <v>682</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -24429,13 +24382,13 @@
       </c>
       <c r="E213" s="2"/>
       <c r="F213" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="G213" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H213" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I213" t="s" s="2">
         <v>73</v>
@@ -24444,20 +24397,18 @@
         <v>82</v>
       </c>
       <c r="K213" t="s" s="2">
-        <v>96</v>
+        <v>128</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>672</v>
+        <v>683</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>635</v>
+        <v>684</v>
       </c>
       <c r="N213" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="O213" t="s" s="2">
-        <v>637</v>
-      </c>
+        <v>685</v>
+      </c>
+      <c r="O213" s="2"/>
       <c r="P213" t="s" s="2">
         <v>73</v>
       </c>
@@ -24481,13 +24432,13 @@
         <v>73</v>
       </c>
       <c r="X213" t="s" s="2">
-        <v>73</v>
+        <v>144</v>
       </c>
       <c r="Y213" t="s" s="2">
-        <v>73</v>
+        <v>686</v>
       </c>
       <c r="Z213" t="s" s="2">
-        <v>73</v>
+        <v>474</v>
       </c>
       <c r="AA213" t="s" s="2">
         <v>73</v>
@@ -24505,7 +24456,7 @@
         <v>73</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>638</v>
+        <v>687</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>74</v>
@@ -24522,10 +24473,10 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>673</v>
+        <v>688</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>639</v>
+        <v>688</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -24542,26 +24493,24 @@
         <v>73</v>
       </c>
       <c r="I214" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="J214" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K214" t="s" s="2">
-        <v>162</v>
+        <v>271</v>
       </c>
       <c r="L214" t="s" s="2">
-        <v>640</v>
+        <v>689</v>
       </c>
       <c r="M214" t="s" s="2">
-        <v>641</v>
+        <v>690</v>
       </c>
       <c r="N214" t="s" s="2">
-        <v>674</v>
-      </c>
-      <c r="O214" t="s" s="2">
-        <v>643</v>
-      </c>
+        <v>691</v>
+      </c>
+      <c r="O214" s="2"/>
       <c r="P214" t="s" s="2">
         <v>73</v>
       </c>
@@ -24585,13 +24534,13 @@
         <v>73</v>
       </c>
       <c r="X214" t="s" s="2">
-        <v>285</v>
+        <v>73</v>
       </c>
       <c r="Y214" t="s" s="2">
-        <v>644</v>
+        <v>73</v>
       </c>
       <c r="Z214" t="s" s="2">
-        <v>645</v>
+        <v>73</v>
       </c>
       <c r="AA214" t="s" s="2">
         <v>73</v>
@@ -24609,7 +24558,7 @@
         <v>73</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>646</v>
+        <v>692</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>74</v>
@@ -24626,10 +24575,10 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>675</v>
+        <v>693</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>647</v>
+        <v>693</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -24652,16 +24601,16 @@
         <v>82</v>
       </c>
       <c r="K215" t="s" s="2">
-        <v>648</v>
+        <v>96</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>649</v>
+        <v>694</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>650</v>
+        <v>695</v>
       </c>
       <c r="N215" t="s" s="2">
-        <v>651</v>
+        <v>696</v>
       </c>
       <c r="O215" s="2"/>
       <c r="P215" t="s" s="2">
@@ -24711,7 +24660,7 @@
         <v>73</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>652</v>
+        <v>697</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>74</v>
@@ -24728,10 +24677,10 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>676</v>
+        <v>698</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>653</v>
+        <v>698</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -24742,7 +24691,7 @@
         <v>74</v>
       </c>
       <c r="G216" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H216" t="s" s="2">
         <v>73</v>
@@ -24751,21 +24700,23 @@
         <v>73</v>
       </c>
       <c r="J216" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K216" t="s" s="2">
-        <v>212</v>
+        <v>699</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>654</v>
+        <v>700</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>655</v>
+        <v>701</v>
       </c>
       <c r="N216" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="O216" s="2"/>
+        <v>702</v>
+      </c>
+      <c r="O216" t="s" s="2">
+        <v>703</v>
+      </c>
       <c r="P216" t="s" s="2">
         <v>73</v>
       </c>
@@ -24813,27 +24764,27 @@
         <v>73</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>656</v>
+        <v>698</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH216" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI216" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ216" t="s" s="2">
-        <v>316</v>
+        <v>94</v>
       </c>
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>677</v>
+        <v>704</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>677</v>
+        <v>704</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -24844,10 +24795,10 @@
         <v>74</v>
       </c>
       <c r="G217" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H217" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I217" t="s" s="2">
         <v>73</v>
@@ -24856,20 +24807,16 @@
         <v>73</v>
       </c>
       <c r="K217" t="s" s="2">
-        <v>678</v>
+        <v>96</v>
       </c>
       <c r="L217" t="s" s="2">
-        <v>679</v>
+        <v>97</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>680</v>
-      </c>
-      <c r="N217" t="s" s="2">
-        <v>681</v>
-      </c>
-      <c r="O217" t="s" s="2">
-        <v>682</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="N217" s="2"/>
+      <c r="O217" s="2"/>
       <c r="P217" t="s" s="2">
         <v>73</v>
       </c>
@@ -24917,38 +24864,38 @@
         <v>73</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>677</v>
+        <v>99</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH217" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI217" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AJ217" t="s" s="2">
-        <v>683</v>
+        <v>73</v>
       </c>
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>684</v>
+        <v>705</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>684</v>
+        <v>705</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="E218" s="2"/>
       <c r="F218" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G218" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H218" t="s" s="2">
         <v>73</v>
@@ -24957,23 +24904,21 @@
         <v>73</v>
       </c>
       <c r="J218" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K218" t="s" s="2">
-        <v>685</v>
+        <v>102</v>
       </c>
       <c r="L218" t="s" s="2">
-        <v>686</v>
+        <v>103</v>
       </c>
       <c r="M218" t="s" s="2">
-        <v>687</v>
+        <v>104</v>
       </c>
       <c r="N218" t="s" s="2">
-        <v>688</v>
-      </c>
-      <c r="O218" t="s" s="2">
-        <v>689</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="O218" s="2"/>
       <c r="P218" t="s" s="2">
         <v>73</v>
       </c>
@@ -25009,71 +24954,75 @@
         <v>73</v>
       </c>
       <c r="AB218" t="s" s="2">
-        <v>73</v>
+        <v>106</v>
       </c>
       <c r="AC218" t="s" s="2">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="AD218" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE218" t="s" s="2">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="AF218" t="s" s="2">
-        <v>684</v>
+        <v>109</v>
       </c>
       <c r="AG218" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH218" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI218" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ218" t="s" s="2">
-        <v>323</v>
+        <v>110</v>
       </c>
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>690</v>
+        <v>706</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>690</v>
+        <v>706</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
-        <v>73</v>
+        <v>707</v>
       </c>
       <c r="E219" s="2"/>
       <c r="F219" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G219" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H219" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I219" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="J219" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K219" t="s" s="2">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="L219" t="s" s="2">
-        <v>97</v>
+        <v>708</v>
       </c>
       <c r="M219" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="N219" s="2"/>
-      <c r="O219" s="2"/>
+        <v>709</v>
+      </c>
+      <c r="N219" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="O219" t="s" s="2">
+        <v>268</v>
+      </c>
       <c r="P219" t="s" s="2">
         <v>73</v>
       </c>
@@ -25121,38 +25070,38 @@
         <v>73</v>
       </c>
       <c r="AF219" t="s" s="2">
-        <v>99</v>
+        <v>710</v>
       </c>
       <c r="AG219" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH219" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI219" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ219" t="s" s="2">
-        <v>73</v>
+        <v>110</v>
       </c>
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>691</v>
+        <v>711</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>691</v>
+        <v>711</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="E220" s="2"/>
       <c r="F220" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G220" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H220" t="s" s="2">
         <v>73</v>
@@ -25164,18 +25113,20 @@
         <v>73</v>
       </c>
       <c r="K220" t="s" s="2">
-        <v>102</v>
+        <v>290</v>
       </c>
       <c r="L220" t="s" s="2">
-        <v>103</v>
+        <v>712</v>
       </c>
       <c r="M220" t="s" s="2">
-        <v>104</v>
+        <v>713</v>
       </c>
       <c r="N220" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="O220" s="2"/>
+        <v>714</v>
+      </c>
+      <c r="O220" t="s" s="2">
+        <v>715</v>
+      </c>
       <c r="P220" t="s" s="2">
         <v>73</v>
       </c>
@@ -25199,51 +25150,51 @@
         <v>73</v>
       </c>
       <c r="X220" t="s" s="2">
-        <v>73</v>
+        <v>144</v>
       </c>
       <c r="Y220" t="s" s="2">
-        <v>73</v>
+        <v>716</v>
       </c>
       <c r="Z220" t="s" s="2">
-        <v>73</v>
+        <v>717</v>
       </c>
       <c r="AA220" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AB220" t="s" s="2">
-        <v>106</v>
+        <v>73</v>
       </c>
       <c r="AC220" t="s" s="2">
-        <v>107</v>
+        <v>73</v>
       </c>
       <c r="AD220" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE220" t="s" s="2">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="AF220" t="s" s="2">
-        <v>109</v>
+        <v>711</v>
       </c>
       <c r="AG220" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH220" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI220" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ220" t="s" s="2">
-        <v>110</v>
+        <v>94</v>
       </c>
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>692</v>
+        <v>718</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>692</v>
+        <v>718</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -25263,21 +25214,23 @@
         <v>73</v>
       </c>
       <c r="J221" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K221" t="s" s="2">
-        <v>96</v>
+        <v>719</v>
       </c>
       <c r="L221" t="s" s="2">
-        <v>693</v>
+        <v>720</v>
       </c>
       <c r="M221" t="s" s="2">
-        <v>694</v>
+        <v>721</v>
       </c>
       <c r="N221" t="s" s="2">
-        <v>695</v>
-      </c>
-      <c r="O221" s="2"/>
+        <v>722</v>
+      </c>
+      <c r="O221" t="s" s="2">
+        <v>723</v>
+      </c>
       <c r="P221" t="s" s="2">
         <v>73</v>
       </c>
@@ -25325,7 +25278,7 @@
         <v>73</v>
       </c>
       <c r="AF221" t="s" s="2">
-        <v>696</v>
+        <v>718</v>
       </c>
       <c r="AG221" t="s" s="2">
         <v>74</v>
@@ -25334,7 +25287,7 @@
         <v>81</v>
       </c>
       <c r="AI221" t="s" s="2">
-        <v>697</v>
+        <v>93</v>
       </c>
       <c r="AJ221" t="s" s="2">
         <v>94</v>
@@ -25342,10 +25295,10 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>698</v>
+        <v>724</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>698</v>
+        <v>724</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -25356,7 +25309,7 @@
         <v>74</v>
       </c>
       <c r="G222" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H222" t="s" s="2">
         <v>73</v>
@@ -25365,21 +25318,21 @@
         <v>73</v>
       </c>
       <c r="J222" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K222" t="s" s="2">
-        <v>128</v>
+        <v>612</v>
       </c>
       <c r="L222" t="s" s="2">
-        <v>699</v>
+        <v>725</v>
       </c>
       <c r="M222" t="s" s="2">
-        <v>700</v>
-      </c>
-      <c r="N222" t="s" s="2">
-        <v>701</v>
-      </c>
-      <c r="O222" s="2"/>
+        <v>614</v>
+      </c>
+      <c r="N222" s="2"/>
+      <c r="O222" t="s" s="2">
+        <v>726</v>
+      </c>
       <c r="P222" t="s" s="2">
         <v>73</v>
       </c>
@@ -25403,13 +25356,13 @@
         <v>73</v>
       </c>
       <c r="X222" t="s" s="2">
-        <v>144</v>
+        <v>73</v>
       </c>
       <c r="Y222" t="s" s="2">
-        <v>702</v>
+        <v>73</v>
       </c>
       <c r="Z222" t="s" s="2">
-        <v>474</v>
+        <v>73</v>
       </c>
       <c r="AA222" t="s" s="2">
         <v>73</v>
@@ -25427,27 +25380,27 @@
         <v>73</v>
       </c>
       <c r="AF222" t="s" s="2">
-        <v>703</v>
+        <v>724</v>
       </c>
       <c r="AG222" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH222" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI222" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ222" t="s" s="2">
-        <v>94</v>
+        <v>727</v>
       </c>
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>704</v>
+        <v>728</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>704</v>
+        <v>728</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -25467,21 +25420,23 @@
         <v>73</v>
       </c>
       <c r="J223" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K223" t="s" s="2">
-        <v>271</v>
+        <v>729</v>
       </c>
       <c r="L223" t="s" s="2">
-        <v>705</v>
+        <v>730</v>
       </c>
       <c r="M223" t="s" s="2">
-        <v>706</v>
+        <v>664</v>
       </c>
       <c r="N223" t="s" s="2">
-        <v>707</v>
-      </c>
-      <c r="O223" s="2"/>
+        <v>665</v>
+      </c>
+      <c r="O223" t="s" s="2">
+        <v>731</v>
+      </c>
       <c r="P223" t="s" s="2">
         <v>73</v>
       </c>
@@ -25529,7 +25484,7 @@
         <v>73</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>708</v>
+        <v>728</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>74</v>
@@ -25546,10 +25501,10 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>709</v>
+        <v>732</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>709</v>
+        <v>732</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -25560,30 +25515,32 @@
         <v>74</v>
       </c>
       <c r="G224" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H224" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I224" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J224" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K224" t="s" s="2">
-        <v>96</v>
+        <v>733</v>
       </c>
       <c r="L224" t="s" s="2">
-        <v>710</v>
+        <v>734</v>
       </c>
       <c r="M224" t="s" s="2">
-        <v>711</v>
+        <v>735</v>
       </c>
       <c r="N224" t="s" s="2">
-        <v>712</v>
-      </c>
-      <c r="O224" s="2"/>
+        <v>672</v>
+      </c>
+      <c r="O224" t="s" s="2">
+        <v>736</v>
+      </c>
       <c r="P224" t="s" s="2">
         <v>73</v>
       </c>
@@ -25631,951 +25588,23 @@
         <v>73</v>
       </c>
       <c r="AF224" t="s" s="2">
-        <v>713</v>
+        <v>732</v>
       </c>
       <c r="AG224" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH224" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI224" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ224" t="s" s="2">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="225" hidden="true">
-      <c r="A225" t="s" s="2">
-        <v>714</v>
-      </c>
-      <c r="B225" t="s" s="2">
-        <v>714</v>
-      </c>
-      <c r="C225" s="2"/>
-      <c r="D225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E225" s="2"/>
-      <c r="F225" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G225" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K225" t="s" s="2">
-        <v>715</v>
-      </c>
-      <c r="L225" t="s" s="2">
-        <v>716</v>
-      </c>
-      <c r="M225" t="s" s="2">
-        <v>717</v>
-      </c>
-      <c r="N225" t="s" s="2">
-        <v>718</v>
-      </c>
-      <c r="O225" t="s" s="2">
-        <v>719</v>
-      </c>
-      <c r="P225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q225" s="2"/>
-      <c r="R225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE225" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF225" t="s" s="2">
-        <v>714</v>
-      </c>
-      <c r="AG225" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH225" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI225" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ225" t="s" s="2">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="226" hidden="true">
-      <c r="A226" t="s" s="2">
-        <v>720</v>
-      </c>
-      <c r="B226" t="s" s="2">
-        <v>720</v>
-      </c>
-      <c r="C226" s="2"/>
-      <c r="D226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E226" s="2"/>
-      <c r="F226" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G226" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K226" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="L226" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="M226" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="N226" s="2"/>
-      <c r="O226" s="2"/>
-      <c r="P226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q226" s="2"/>
-      <c r="R226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF226" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AG226" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH226" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI226" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ226" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="227" hidden="true">
-      <c r="A227" t="s" s="2">
-        <v>721</v>
-      </c>
-      <c r="B227" t="s" s="2">
-        <v>721</v>
-      </c>
-      <c r="C227" s="2"/>
-      <c r="D227" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="E227" s="2"/>
-      <c r="F227" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G227" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K227" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="L227" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="M227" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N227" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="O227" s="2"/>
-      <c r="P227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q227" s="2"/>
-      <c r="R227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB227" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AC227" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AD227" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE227" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AF227" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AG227" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH227" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI227" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ227" t="s" s="2">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="228" hidden="true">
-      <c r="A228" t="s" s="2">
-        <v>722</v>
-      </c>
-      <c r="B228" t="s" s="2">
-        <v>722</v>
-      </c>
-      <c r="C228" s="2"/>
-      <c r="D228" t="s" s="2">
-        <v>723</v>
-      </c>
-      <c r="E228" s="2"/>
-      <c r="F228" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G228" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I228" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J228" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K228" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="L228" t="s" s="2">
-        <v>724</v>
-      </c>
-      <c r="M228" t="s" s="2">
-        <v>725</v>
-      </c>
-      <c r="N228" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="O228" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="P228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q228" s="2"/>
-      <c r="R228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE228" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF228" t="s" s="2">
-        <v>726</v>
-      </c>
-      <c r="AG228" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH228" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI228" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ228" t="s" s="2">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="229" hidden="true">
-      <c r="A229" t="s" s="2">
-        <v>727</v>
-      </c>
-      <c r="B229" t="s" s="2">
-        <v>727</v>
-      </c>
-      <c r="C229" s="2"/>
-      <c r="D229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E229" s="2"/>
-      <c r="F229" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G229" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K229" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="L229" t="s" s="2">
-        <v>728</v>
-      </c>
-      <c r="M229" t="s" s="2">
-        <v>729</v>
-      </c>
-      <c r="N229" t="s" s="2">
-        <v>730</v>
-      </c>
-      <c r="O229" t="s" s="2">
-        <v>731</v>
-      </c>
-      <c r="P229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q229" s="2"/>
-      <c r="R229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X229" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="Y229" t="s" s="2">
-        <v>732</v>
-      </c>
-      <c r="Z229" t="s" s="2">
-        <v>733</v>
-      </c>
-      <c r="AA229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE229" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF229" t="s" s="2">
-        <v>727</v>
-      </c>
-      <c r="AG229" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH229" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI229" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ229" t="s" s="2">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="230" hidden="true">
-      <c r="A230" t="s" s="2">
-        <v>734</v>
-      </c>
-      <c r="B230" t="s" s="2">
-        <v>734</v>
-      </c>
-      <c r="C230" s="2"/>
-      <c r="D230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E230" s="2"/>
-      <c r="F230" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G230" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K230" t="s" s="2">
-        <v>735</v>
-      </c>
-      <c r="L230" t="s" s="2">
-        <v>736</v>
-      </c>
-      <c r="M230" t="s" s="2">
-        <v>737</v>
-      </c>
-      <c r="N230" t="s" s="2">
-        <v>738</v>
-      </c>
-      <c r="O230" t="s" s="2">
-        <v>739</v>
-      </c>
-      <c r="P230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q230" s="2"/>
-      <c r="R230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE230" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF230" t="s" s="2">
-        <v>734</v>
-      </c>
-      <c r="AG230" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH230" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI230" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ230" t="s" s="2">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="231" hidden="true">
-      <c r="A231" t="s" s="2">
-        <v>740</v>
-      </c>
-      <c r="B231" t="s" s="2">
-        <v>740</v>
-      </c>
-      <c r="C231" s="2"/>
-      <c r="D231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E231" s="2"/>
-      <c r="F231" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G231" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K231" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="L231" t="s" s="2">
-        <v>741</v>
-      </c>
-      <c r="M231" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="N231" s="2"/>
-      <c r="O231" t="s" s="2">
-        <v>742</v>
-      </c>
-      <c r="P231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q231" s="2"/>
-      <c r="R231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF231" t="s" s="2">
-        <v>740</v>
-      </c>
-      <c r="AG231" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH231" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI231" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ231" t="s" s="2">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="232" hidden="true">
-      <c r="A232" t="s" s="2">
-        <v>744</v>
-      </c>
-      <c r="B232" t="s" s="2">
-        <v>744</v>
-      </c>
-      <c r="C232" s="2"/>
-      <c r="D232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E232" s="2"/>
-      <c r="F232" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G232" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K232" t="s" s="2">
-        <v>745</v>
-      </c>
-      <c r="L232" t="s" s="2">
-        <v>746</v>
-      </c>
-      <c r="M232" t="s" s="2">
-        <v>680</v>
-      </c>
-      <c r="N232" t="s" s="2">
-        <v>681</v>
-      </c>
-      <c r="O232" t="s" s="2">
-        <v>747</v>
-      </c>
-      <c r="P232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q232" s="2"/>
-      <c r="R232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE232" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF232" t="s" s="2">
-        <v>744</v>
-      </c>
-      <c r="AG232" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH232" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI232" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ232" t="s" s="2">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="233" hidden="true">
-      <c r="A233" t="s" s="2">
-        <v>748</v>
-      </c>
-      <c r="B233" t="s" s="2">
-        <v>748</v>
-      </c>
-      <c r="C233" s="2"/>
-      <c r="D233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E233" s="2"/>
-      <c r="F233" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G233" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H233" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K233" t="s" s="2">
-        <v>749</v>
-      </c>
-      <c r="L233" t="s" s="2">
-        <v>750</v>
-      </c>
-      <c r="M233" t="s" s="2">
-        <v>751</v>
-      </c>
-      <c r="N233" t="s" s="2">
-        <v>688</v>
-      </c>
-      <c r="O233" t="s" s="2">
-        <v>752</v>
-      </c>
-      <c r="P233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q233" s="2"/>
-      <c r="R233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE233" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF233" t="s" s="2">
-        <v>748</v>
-      </c>
-      <c r="AG233" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH233" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI233" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ233" t="s" s="2">
         <v>323</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ233">
+  <autoFilter ref="A1:AJ224">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -26585,7 +25614,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI232">
+  <conditionalFormatting sqref="A2:AI223">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/nr-add-mapping/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T13:59:51+00:00</t>
+    <t>2024-04-03T14:08:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-mapping/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-dr-organization.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8078" uniqueCount="808">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8078" uniqueCount="821">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T14:18:25+00:00</t>
+    <t>2024-04-03T14:35:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -275,7 +275,7 @@
 dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}org-1:The organization SHALL at least have a name or an identifier, and possibly more than one {(identifier.count() + name.count()) &gt; 0}</t>
   </si>
   <si>
-    <t>EntiteJuridique</t>
+    <t>EntiteGeographique</t>
   </si>
   <si>
     <t>(also see master files messages)</t>
@@ -785,6 +785,9 @@
 per-1</t>
   </si>
   <si>
+    <t>dateCreation</t>
+  </si>
+  <si>
     <t>DR.1</t>
   </si>
   <si>
@@ -810,6 +813,9 @@
   </si>
   <si>
     <t>Period.end</t>
+  </si>
+  <si>
+    <t>dateFermeture</t>
   </si>
   <si>
     <t>DR.2</t>
@@ -850,6 +856,9 @@
     <t>Extension créée dans le cadre de l'Annuaire Santé pour prise en compte de la licence d’exploitation d’une officine.</t>
   </si>
   <si>
+    <t>numeroLicenceOfficine</t>
+  </si>
+  <si>
     <t>Organization.extension:as-ext-organization-pricing-model</t>
   </si>
   <si>
@@ -882,6 +891,9 @@
     <t>Extension créée dans le cadre de l'Annuaire Santé pour prise en compte du type de fermeture de la structure.</t>
   </si>
   <si>
+    <t>typeFermeture</t>
+  </si>
+  <si>
     <t>Organization.extension:as-ext-organization-budget-type</t>
   </si>
   <si>
@@ -976,6 +988,9 @@
   </si>
   <si>
     <t>Identifiant idNat_Struct délivré par une autorité d'enregistrement tel que défini dans l'Annexe Transverse Source des données métier pour les professionnels et les structures.</t>
+  </si>
+  <si>
+    <t>idNat_struct</t>
   </si>
   <si>
     <t>Organization.identifier:idNatSt.id</t>
@@ -1198,6 +1213,9 @@
     <t>Identifiant SIREN (9 chiffres) ou SIRET (14 chiffres)</t>
   </si>
   <si>
+    <t>numSiren</t>
+  </si>
+  <si>
     <t>Organization.identifier:sirene.id</t>
   </si>
   <si>
@@ -1893,6 +1911,9 @@
     <t>https://mos.esante.gouv.fr/NOS/JDV_J99-InseeNAFrav2Niveau5-RASS/FHIR/JDV-J99-InseeNAFrav2Niveau5-RASS</t>
   </si>
   <si>
+    <t>codeAPEN</t>
+  </si>
+  <si>
     <t>Organization.type:activiteINSEE.id</t>
   </si>
   <si>
@@ -1932,6 +1953,9 @@
     <t>https://mos.esante.gouv.fr/NOS/JDV_J100-FinessStatutJuridique-RASS/FHIR/JDV-J100-FinessStatutJuridique-RASS</t>
   </si>
   <si>
+    <t>statutJuridique</t>
+  </si>
+  <si>
     <t>Organization.type:statutJuridiqueINSEE.id</t>
   </si>
   <si>
@@ -2047,6 +2071,9 @@
   </si>
   <si>
     <t>Need to use the name as the label of the organization.</t>
+  </si>
+  <si>
+    <t>raisonSociale</t>
   </si>
   <si>
     <t>XON.1</t>
@@ -2074,6 +2101,9 @@
 For searching knowing previous names that the organization was known by can be very useful.</t>
   </si>
   <si>
+    <t>raisonSocialeLongue</t>
+  </si>
+  <si>
     <t>Organization.telecom</t>
   </si>
   <si>
@@ -2101,6 +2131,9 @@
 ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}org-3:The telecom of an organization can never be of use 'home' {where(use = 'home').empty()}</t>
   </si>
   <si>
+    <t>telecommunication</t>
+  </si>
+  <si>
     <t>XTN</t>
   </si>
   <si>
@@ -2267,6 +2300,9 @@
     <t>Les BALs MSS de type ORG ou APP rattachées à une personne morale responsable de l’accès et de l’usage de la BAL (boiteLettreMSS).</t>
   </si>
   <si>
+    <t>boiteLettreMSS</t>
+  </si>
+  <si>
     <t>Organization.address</t>
   </si>
   <si>
@@ -2288,6 +2324,9 @@
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 org-2:An address of an organization can never be of use 'home' {where(use = 'home').empty()}</t>
+  </si>
+  <si>
+    <t>adresseEJ</t>
   </si>
   <si>
     <t>XAD</t>
@@ -6256,13 +6295,13 @@
         <v>101</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>78</v>
+        <v>246</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>78</v>
@@ -6273,10 +6312,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6302,20 +6341,20 @@
         <v>240</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q30" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="R30" t="s" s="2">
         <v>78</v>
@@ -6360,7 +6399,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -6375,13 +6414,13 @@
         <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>78</v>
+        <v>256</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>78</v>
@@ -6392,13 +6431,13 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>199</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D31" t="s" s="2">
         <v>78</v>
@@ -6420,13 +6459,13 @@
         <v>78</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -6509,13 +6548,13 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>199</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D32" t="s" s="2">
         <v>78</v>
@@ -6537,13 +6576,13 @@
         <v>78</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6609,7 +6648,7 @@
         <v>118</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>78</v>
+        <v>269</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>78</v>
@@ -6626,13 +6665,13 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>199</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="D33" t="s" s="2">
         <v>78</v>
@@ -6654,13 +6693,13 @@
         <v>78</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6743,13 +6782,13 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>199</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>78</v>
@@ -6771,13 +6810,13 @@
         <v>78</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6843,7 +6882,7 @@
         <v>118</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>78</v>
+        <v>280</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>78</v>
@@ -6860,13 +6899,13 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>199</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="D35" t="s" s="2">
         <v>78</v>
@@ -6888,13 +6927,13 @@
         <v>78</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6977,13 +7016,13 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>199</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="D36" t="s" s="2">
         <v>78</v>
@@ -7005,13 +7044,13 @@
         <v>78</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -7094,10 +7133,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7123,16 +7162,16 @@
         <v>110</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="N37" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>78</v>
@@ -7181,7 +7220,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -7213,10 +7252,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7239,17 +7278,17 @@
         <v>90</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>78</v>
@@ -7286,10 +7325,10 @@
         <v>78</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>78</v>
@@ -7298,7 +7337,7 @@
         <v>116</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -7307,7 +7346,7 @@
         <v>80</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>101</v>
@@ -7316,27 +7355,27 @@
         <v>78</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>78</v>
@@ -7358,17 +7397,17 @@
         <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>78</v>
@@ -7417,7 +7456,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -7426,33 +7465,33 @@
         <v>80</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>78</v>
+        <v>311</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7564,10 +7603,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7681,10 +7720,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7710,16 +7749,16 @@
         <v>175</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>78</v>
@@ -7729,7 +7768,7 @@
         <v>78</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>78</v>
@@ -7744,13 +7783,13 @@
         <v>78</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>78</v>
@@ -7768,7 +7807,7 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -7789,7 +7828,7 @@
         <v>198</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>78</v>
@@ -7800,10 +7839,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7826,19 +7865,19 @@
         <v>90</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>78</v>
@@ -7848,7 +7887,7 @@
         <v>78</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>78</v>
@@ -7866,10 +7905,10 @@
         <v>157</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>78</v>
@@ -7887,7 +7926,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -7905,10 +7944,10 @@
         <v>78</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>78</v>
@@ -7919,10 +7958,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7948,16 +7987,16 @@
         <v>136</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>78</v>
@@ -7967,10 +8006,10 @@
         <v>78</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="U44" t="s" s="2">
         <v>78</v>
@@ -8006,7 +8045,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -8024,13 +8063,13 @@
         <v>78</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>78</v>
@@ -8038,10 +8077,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8067,13 +8106,13 @@
         <v>103</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -8087,7 +8126,7 @@
         <v>78</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="U45" t="s" s="2">
         <v>78</v>
@@ -8123,7 +8162,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -8141,13 +8180,13 @@
         <v>78</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>78</v>
@@ -8155,10 +8194,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8184,10 +8223,10 @@
         <v>230</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -8238,7 +8277,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -8256,13 +8295,13 @@
         <v>78</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>78</v>
@@ -8270,10 +8309,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8296,16 +8335,16 @@
         <v>90</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8355,7 +8394,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -8373,13 +8412,13 @@
         <v>78</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>78</v>
@@ -8387,13 +8426,13 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>78</v>
@@ -8415,17 +8454,17 @@
         <v>90</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>78</v>
@@ -8474,7 +8513,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -8483,33 +8522,33 @@
         <v>80</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>78</v>
+        <v>383</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8621,10 +8660,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8738,10 +8777,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8767,16 +8806,16 @@
         <v>175</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>78</v>
@@ -8801,13 +8840,13 @@
         <v>78</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>78</v>
@@ -8825,7 +8864,7 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -8846,7 +8885,7 @@
         <v>198</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>78</v>
@@ -8857,10 +8896,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8883,19 +8922,19 @@
         <v>90</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>78</v>
@@ -8923,10 +8962,10 @@
         <v>157</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>78</v>
@@ -8944,7 +8983,7 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -8962,10 +9001,10 @@
         <v>78</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>78</v>
@@ -8976,10 +9015,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9091,10 +9130,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9208,10 +9247,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9237,16 +9276,16 @@
         <v>153</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>78</v>
@@ -9295,7 +9334,7 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -9313,10 +9352,10 @@
         <v>78</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>78</v>
@@ -9327,10 +9366,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9442,10 +9481,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9559,10 +9598,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9588,16 +9627,16 @@
         <v>136</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>78</v>
@@ -9607,7 +9646,7 @@
         <v>78</v>
       </c>
       <c r="S58" t="s" s="2">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="T58" t="s" s="2">
         <v>78</v>
@@ -9646,7 +9685,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -9664,10 +9703,10 @@
         <v>78</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>78</v>
@@ -9678,10 +9717,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9707,13 +9746,13 @@
         <v>103</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9763,7 +9802,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -9781,10 +9820,10 @@
         <v>78</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>78</v>
@@ -9795,10 +9834,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9824,14 +9863,14 @@
         <v>175</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>78</v>
@@ -9880,7 +9919,7 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9898,10 +9937,10 @@
         <v>78</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>78</v>
@@ -9912,10 +9951,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9941,14 +9980,14 @@
         <v>103</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>78</v>
@@ -9997,7 +10036,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -10015,10 +10054,10 @@
         <v>78</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>78</v>
@@ -10029,10 +10068,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10055,19 +10094,19 @@
         <v>90</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>78</v>
@@ -10116,7 +10155,7 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -10134,10 +10173,10 @@
         <v>78</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>78</v>
@@ -10148,10 +10187,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10177,16 +10216,16 @@
         <v>103</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>78</v>
@@ -10235,7 +10274,7 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -10253,10 +10292,10 @@
         <v>78</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>78</v>
@@ -10267,10 +10306,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10296,16 +10335,16 @@
         <v>136</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>78</v>
@@ -10315,10 +10354,10 @@
         <v>78</v>
       </c>
       <c r="S64" t="s" s="2">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="T64" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="U64" t="s" s="2">
         <v>78</v>
@@ -10354,7 +10393,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -10372,13 +10411,13 @@
         <v>78</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>78</v>
@@ -10386,10 +10425,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10415,13 +10454,13 @@
         <v>103</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10435,7 +10474,7 @@
         <v>78</v>
       </c>
       <c r="T65" t="s" s="2">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="U65" t="s" s="2">
         <v>78</v>
@@ -10471,7 +10510,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -10489,13 +10528,13 @@
         <v>78</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>78</v>
@@ -10503,10 +10542,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10532,10 +10571,10 @@
         <v>230</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10586,7 +10625,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -10604,13 +10643,13 @@
         <v>78</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>78</v>
@@ -10618,10 +10657,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10644,16 +10683,16 @@
         <v>90</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10703,7 +10742,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -10721,13 +10760,13 @@
         <v>78</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>78</v>
@@ -10735,13 +10774,13 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="D68" t="s" s="2">
         <v>78</v>
@@ -10763,17 +10802,17 @@
         <v>90</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>78</v>
@@ -10822,7 +10861,7 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -10831,33 +10870,33 @@
         <v>80</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10969,10 +11008,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11086,10 +11125,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11115,16 +11154,16 @@
         <v>175</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>78</v>
@@ -11149,13 +11188,13 @@
         <v>78</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>78</v>
@@ -11173,7 +11212,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -11194,7 +11233,7 @@
         <v>198</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>78</v>
@@ -11205,10 +11244,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11231,19 +11270,19 @@
         <v>90</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>78</v>
@@ -11271,10 +11310,10 @@
         <v>157</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>78</v>
@@ -11292,7 +11331,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -11310,10 +11349,10 @@
         <v>78</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>78</v>
@@ -11324,10 +11363,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11439,10 +11478,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11556,10 +11595,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11585,16 +11624,16 @@
         <v>153</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>78</v>
@@ -11643,7 +11682,7 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -11661,10 +11700,10 @@
         <v>78</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>78</v>
@@ -11675,10 +11714,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11790,10 +11829,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11907,10 +11946,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11936,16 +11975,16 @@
         <v>136</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>78</v>
@@ -11955,7 +11994,7 @@
         <v>78</v>
       </c>
       <c r="S78" t="s" s="2">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="T78" t="s" s="2">
         <v>78</v>
@@ -11994,7 +12033,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -12012,10 +12051,10 @@
         <v>78</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>78</v>
@@ -12026,10 +12065,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12055,13 +12094,13 @@
         <v>103</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -12111,7 +12150,7 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -12129,10 +12168,10 @@
         <v>78</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>78</v>
@@ -12143,10 +12182,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12172,14 +12211,14 @@
         <v>175</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>78</v>
@@ -12228,7 +12267,7 @@
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -12246,10 +12285,10 @@
         <v>78</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>78</v>
@@ -12260,10 +12299,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12289,14 +12328,14 @@
         <v>103</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" t="s" s="2">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>78</v>
@@ -12345,7 +12384,7 @@
         <v>78</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -12363,10 +12402,10 @@
         <v>78</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>78</v>
@@ -12377,10 +12416,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12403,19 +12442,19 @@
         <v>90</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>78</v>
@@ -12464,7 +12503,7 @@
         <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -12482,10 +12521,10 @@
         <v>78</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>78</v>
@@ -12496,10 +12535,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12525,16 +12564,16 @@
         <v>103</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>78</v>
@@ -12583,7 +12622,7 @@
         <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -12601,10 +12640,10 @@
         <v>78</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>78</v>
@@ -12615,10 +12654,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12644,16 +12683,16 @@
         <v>136</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>78</v>
@@ -12663,10 +12702,10 @@
         <v>78</v>
       </c>
       <c r="S84" t="s" s="2">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="T84" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="U84" t="s" s="2">
         <v>78</v>
@@ -12702,7 +12741,7 @@
         <v>78</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -12720,13 +12759,13 @@
         <v>78</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>78</v>
@@ -12734,10 +12773,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12763,13 +12802,13 @@
         <v>103</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12783,7 +12822,7 @@
         <v>78</v>
       </c>
       <c r="T85" t="s" s="2">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="U85" t="s" s="2">
         <v>78</v>
@@ -12819,7 +12858,7 @@
         <v>78</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
@@ -12837,13 +12876,13 @@
         <v>78</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>78</v>
@@ -12851,10 +12890,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12880,10 +12919,10 @@
         <v>230</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12934,7 +12973,7 @@
         <v>78</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -12952,13 +12991,13 @@
         <v>78</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>78</v>
@@ -12966,10 +13005,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12992,16 +13031,16 @@
         <v>90</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -13051,7 +13090,7 @@
         <v>78</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
@@ -13069,13 +13108,13 @@
         <v>78</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>78</v>
@@ -13083,13 +13122,13 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="D88" t="s" s="2">
         <v>78</v>
@@ -13111,17 +13150,17 @@
         <v>90</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>78</v>
@@ -13170,7 +13209,7 @@
         <v>78</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -13179,7 +13218,7 @@
         <v>80</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>101</v>
@@ -13188,24 +13227,24 @@
         <v>78</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13317,10 +13356,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13434,10 +13473,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13463,16 +13502,16 @@
         <v>175</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>78</v>
@@ -13497,13 +13536,13 @@
         <v>78</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>78</v>
@@ -13521,7 +13560,7 @@
         <v>78</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -13542,7 +13581,7 @@
         <v>198</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>78</v>
@@ -13553,10 +13592,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13579,19 +13618,19 @@
         <v>90</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>78</v>
@@ -13601,7 +13640,7 @@
         <v>78</v>
       </c>
       <c r="S92" t="s" s="2">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="T92" t="s" s="2">
         <v>78</v>
@@ -13619,10 +13658,10 @@
         <v>157</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>78</v>
@@ -13640,7 +13679,7 @@
         <v>78</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -13658,10 +13697,10 @@
         <v>78</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>78</v>
@@ -13672,10 +13711,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13701,16 +13740,16 @@
         <v>136</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>78</v>
@@ -13720,10 +13759,10 @@
         <v>78</v>
       </c>
       <c r="S93" t="s" s="2">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="T93" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="U93" t="s" s="2">
         <v>78</v>
@@ -13759,7 +13798,7 @@
         <v>78</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -13777,13 +13816,13 @@
         <v>78</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>78</v>
@@ -13791,10 +13830,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13820,13 +13859,13 @@
         <v>103</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13840,7 +13879,7 @@
         <v>78</v>
       </c>
       <c r="T94" t="s" s="2">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="U94" t="s" s="2">
         <v>78</v>
@@ -13876,7 +13915,7 @@
         <v>78</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -13894,13 +13933,13 @@
         <v>78</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>78</v>
@@ -13908,10 +13947,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13937,10 +13976,10 @@
         <v>230</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -13991,7 +14030,7 @@
         <v>78</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
@@ -14009,13 +14048,13 @@
         <v>78</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>78</v>
@@ -14023,10 +14062,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14049,16 +14088,16 @@
         <v>90</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -14108,7 +14147,7 @@
         <v>78</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -14126,13 +14165,13 @@
         <v>78</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>78</v>
@@ -14140,13 +14179,13 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D97" t="s" s="2">
         <v>78</v>
@@ -14168,17 +14207,17 @@
         <v>90</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" t="s" s="2">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>78</v>
@@ -14227,7 +14266,7 @@
         <v>78</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -14236,7 +14275,7 @@
         <v>80</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="AJ97" t="s" s="2">
         <v>101</v>
@@ -14245,24 +14284,24 @@
         <v>78</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14374,10 +14413,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14491,10 +14530,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14520,16 +14559,16 @@
         <v>175</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>78</v>
@@ -14554,13 +14593,13 @@
         <v>78</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>78</v>
@@ -14578,7 +14617,7 @@
         <v>78</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
@@ -14599,7 +14638,7 @@
         <v>198</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>78</v>
@@ -14610,10 +14649,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14636,19 +14675,19 @@
         <v>90</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>78</v>
@@ -14658,7 +14697,7 @@
         <v>78</v>
       </c>
       <c r="S101" t="s" s="2">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="T101" t="s" s="2">
         <v>78</v>
@@ -14676,10 +14715,10 @@
         <v>157</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>78</v>
@@ -14697,7 +14736,7 @@
         <v>78</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
@@ -14715,10 +14754,10 @@
         <v>78</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>78</v>
@@ -14729,10 +14768,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14758,16 +14797,16 @@
         <v>136</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>78</v>
@@ -14777,10 +14816,10 @@
         <v>78</v>
       </c>
       <c r="S102" t="s" s="2">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="T102" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="U102" t="s" s="2">
         <v>78</v>
@@ -14816,7 +14855,7 @@
         <v>78</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
@@ -14834,13 +14873,13 @@
         <v>78</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>78</v>
@@ -14848,10 +14887,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14877,13 +14916,13 @@
         <v>103</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -14897,7 +14936,7 @@
         <v>78</v>
       </c>
       <c r="T103" t="s" s="2">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="U103" t="s" s="2">
         <v>78</v>
@@ -14933,7 +14972,7 @@
         <v>78</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
@@ -14951,13 +14990,13 @@
         <v>78</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>78</v>
@@ -14965,10 +15004,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14994,10 +15033,10 @@
         <v>230</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -15048,7 +15087,7 @@
         <v>78</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
@@ -15066,13 +15105,13 @@
         <v>78</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>78</v>
@@ -15080,10 +15119,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15106,16 +15145,16 @@
         <v>90</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -15165,7 +15204,7 @@
         <v>78</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
@@ -15183,13 +15222,13 @@
         <v>78</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>78</v>
@@ -15197,10 +15236,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15223,25 +15262,25 @@
         <v>90</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q106" t="s" s="2">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="R106" t="s" s="2">
         <v>78</v>
@@ -15286,7 +15325,7 @@
         <v>78</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
@@ -15304,24 +15343,24 @@
         <v>78</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="AO106" t="s" s="2">
-        <v>517</v>
+        <v>523</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15344,19 +15383,19 @@
         <v>90</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>78</v>
@@ -15384,16 +15423,16 @@
         <v>165</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB107" t="s" s="2">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="AC107" s="2"/>
       <c r="AD107" t="s" s="2">
@@ -15403,7 +15442,7 @@
         <v>116</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>79</v>
@@ -15421,27 +15460,27 @@
         <v>78</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>528</v>
+        <v>534</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="D108" t="s" s="2">
         <v>78</v>
@@ -15463,19 +15502,19 @@
         <v>90</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>78</v>
@@ -15500,11 +15539,11 @@
         <v>78</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="Y108" s="2"/>
       <c r="Z108" t="s" s="2">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>78</v>
@@ -15522,7 +15561,7 @@
         <v>78</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>79</v>
@@ -15540,24 +15579,24 @@
         <v>78</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>528</v>
+        <v>534</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15669,10 +15708,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15784,13 +15823,13 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="D111" t="s" s="2">
         <v>78</v>
@@ -15812,13 +15851,13 @@
         <v>78</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -15901,10 +15940,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16016,10 +16055,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16131,10 +16170,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16174,7 +16213,7 @@
       </c>
       <c r="Q114" s="2"/>
       <c r="R114" t="s" s="2">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="S114" t="s" s="2">
         <v>78</v>
@@ -16248,10 +16287,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16292,7 +16331,7 @@
         <v>78</v>
       </c>
       <c r="S115" t="s" s="2">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="T115" t="s" s="2">
         <v>78</v>
@@ -16307,11 +16346,11 @@
         <v>78</v>
       </c>
       <c r="X115" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="Y115" s="2"/>
       <c r="Z115" t="s" s="2">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>78</v>
@@ -16361,10 +16400,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16390,16 +16429,16 @@
         <v>153</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>78</v>
@@ -16448,7 +16487,7 @@
         <v>78</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>79</v>
@@ -16466,10 +16505,10 @@
         <v>78</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="AN116" t="s" s="2">
         <v>78</v>
@@ -16480,10 +16519,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16595,10 +16634,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16712,10 +16751,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16741,16 +16780,16 @@
         <v>136</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>78</v>
@@ -16799,7 +16838,7 @@
         <v>78</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>79</v>
@@ -16817,10 +16856,10 @@
         <v>78</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="AN119" t="s" s="2">
         <v>78</v>
@@ -16831,10 +16870,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16860,13 +16899,13 @@
         <v>103</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
@@ -16916,7 +16955,7 @@
         <v>78</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>79</v>
@@ -16934,10 +16973,10 @@
         <v>78</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="AN120" t="s" s="2">
         <v>78</v>
@@ -16948,10 +16987,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16977,14 +17016,14 @@
         <v>175</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" t="s" s="2">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>78</v>
@@ -17033,7 +17072,7 @@
         <v>78</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>79</v>
@@ -17051,10 +17090,10 @@
         <v>78</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="AN121" t="s" s="2">
         <v>78</v>
@@ -17065,10 +17104,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17094,14 +17133,14 @@
         <v>103</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" t="s" s="2">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>78</v>
@@ -17150,7 +17189,7 @@
         <v>78</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>79</v>
@@ -17168,10 +17207,10 @@
         <v>78</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="AN122" t="s" s="2">
         <v>78</v>
@@ -17182,10 +17221,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17208,19 +17247,19 @@
         <v>90</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>78</v>
@@ -17269,7 +17308,7 @@
         <v>78</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>79</v>
@@ -17287,10 +17326,10 @@
         <v>78</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="AN123" t="s" s="2">
         <v>78</v>
@@ -17301,10 +17340,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17330,16 +17369,16 @@
         <v>103</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>78</v>
@@ -17388,7 +17427,7 @@
         <v>78</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>79</v>
@@ -17406,10 +17445,10 @@
         <v>78</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="AN124" t="s" s="2">
         <v>78</v>
@@ -17420,13 +17459,13 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="D125" t="s" s="2">
         <v>78</v>
@@ -17448,19 +17487,19 @@
         <v>90</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>78</v>
@@ -17485,11 +17524,11 @@
         <v>78</v>
       </c>
       <c r="X125" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="Y125" s="2"/>
       <c r="Z125" t="s" s="2">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>78</v>
@@ -17507,7 +17546,7 @@
         <v>78</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>79</v>
@@ -17525,24 +17564,24 @@
         <v>78</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="AN125" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AO125" t="s" s="2">
-        <v>528</v>
+        <v>534</v>
       </c>
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17654,10 +17693,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17771,10 +17810,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17800,16 +17839,16 @@
         <v>153</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="O128" t="s" s="2">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>78</v>
@@ -17858,7 +17897,7 @@
         <v>78</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>79</v>
@@ -17876,10 +17915,10 @@
         <v>78</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="AN128" t="s" s="2">
         <v>78</v>
@@ -17890,10 +17929,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18005,10 +18044,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18122,10 +18161,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18151,16 +18190,16 @@
         <v>136</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>78</v>
@@ -18209,7 +18248,7 @@
         <v>78</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>79</v>
@@ -18227,10 +18266,10 @@
         <v>78</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="AN131" t="s" s="2">
         <v>78</v>
@@ -18241,10 +18280,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18270,13 +18309,13 @@
         <v>103</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -18326,7 +18365,7 @@
         <v>78</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>79</v>
@@ -18344,10 +18383,10 @@
         <v>78</v>
       </c>
       <c r="AL132" t="s" s="2">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="AN132" t="s" s="2">
         <v>78</v>
@@ -18358,10 +18397,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18387,14 +18426,14 @@
         <v>175</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" t="s" s="2">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>78</v>
@@ -18443,7 +18482,7 @@
         <v>78</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>79</v>
@@ -18461,10 +18500,10 @@
         <v>78</v>
       </c>
       <c r="AL133" t="s" s="2">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="AN133" t="s" s="2">
         <v>78</v>
@@ -18475,10 +18514,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18504,14 +18543,14 @@
         <v>103</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" t="s" s="2">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>78</v>
@@ -18560,7 +18599,7 @@
         <v>78</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>79</v>
@@ -18578,10 +18617,10 @@
         <v>78</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="AM134" t="s" s="2">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="AN134" t="s" s="2">
         <v>78</v>
@@ -18592,10 +18631,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18618,19 +18657,19 @@
         <v>90</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>78</v>
@@ -18679,7 +18718,7 @@
         <v>78</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>79</v>
@@ -18697,10 +18736,10 @@
         <v>78</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="AN135" t="s" s="2">
         <v>78</v>
@@ -18711,10 +18750,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18740,16 +18779,16 @@
         <v>103</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>78</v>
@@ -18798,7 +18837,7 @@
         <v>78</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>79</v>
@@ -18816,10 +18855,10 @@
         <v>78</v>
       </c>
       <c r="AL136" t="s" s="2">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="AN136" t="s" s="2">
         <v>78</v>
@@ -18830,13 +18869,13 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="D137" t="s" s="2">
         <v>78</v>
@@ -18858,19 +18897,19 @@
         <v>90</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>78</v>
@@ -18895,11 +18934,11 @@
         <v>78</v>
       </c>
       <c r="X137" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="Y137" s="2"/>
       <c r="Z137" t="s" s="2">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="AA137" t="s" s="2">
         <v>78</v>
@@ -18917,7 +18956,7 @@
         <v>78</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>79</v>
@@ -18935,24 +18974,24 @@
         <v>78</v>
       </c>
       <c r="AL137" t="s" s="2">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="AN137" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AO137" t="s" s="2">
-        <v>528</v>
+        <v>534</v>
       </c>
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19064,10 +19103,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19181,10 +19220,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19210,16 +19249,16 @@
         <v>153</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="O140" t="s" s="2">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>78</v>
@@ -19268,7 +19307,7 @@
         <v>78</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>79</v>
@@ -19286,10 +19325,10 @@
         <v>78</v>
       </c>
       <c r="AL140" t="s" s="2">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="AM140" t="s" s="2">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="AN140" t="s" s="2">
         <v>78</v>
@@ -19300,10 +19339,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19415,10 +19454,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19532,10 +19571,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19561,16 +19600,16 @@
         <v>136</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="O143" t="s" s="2">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>78</v>
@@ -19619,7 +19658,7 @@
         <v>78</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>79</v>
@@ -19637,10 +19676,10 @@
         <v>78</v>
       </c>
       <c r="AL143" t="s" s="2">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="AN143" t="s" s="2">
         <v>78</v>
@@ -19651,10 +19690,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19680,13 +19719,13 @@
         <v>103</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
@@ -19736,7 +19775,7 @@
         <v>78</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>79</v>
@@ -19754,10 +19793,10 @@
         <v>78</v>
       </c>
       <c r="AL144" t="s" s="2">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="AM144" t="s" s="2">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="AN144" t="s" s="2">
         <v>78</v>
@@ -19768,10 +19807,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19797,14 +19836,14 @@
         <v>175</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" t="s" s="2">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>78</v>
@@ -19853,7 +19892,7 @@
         <v>78</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>79</v>
@@ -19871,10 +19910,10 @@
         <v>78</v>
       </c>
       <c r="AL145" t="s" s="2">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="AM145" t="s" s="2">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="AN145" t="s" s="2">
         <v>78</v>
@@ -19885,10 +19924,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19914,14 +19953,14 @@
         <v>103</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" t="s" s="2">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>78</v>
@@ -19970,7 +20009,7 @@
         <v>78</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>79</v>
@@ -19988,10 +20027,10 @@
         <v>78</v>
       </c>
       <c r="AL146" t="s" s="2">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="AM146" t="s" s="2">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="AN146" t="s" s="2">
         <v>78</v>
@@ -20002,10 +20041,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20028,19 +20067,19 @@
         <v>90</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="O147" t="s" s="2">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>78</v>
@@ -20089,7 +20128,7 @@
         <v>78</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>79</v>
@@ -20107,10 +20146,10 @@
         <v>78</v>
       </c>
       <c r="AL147" t="s" s="2">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="AM147" t="s" s="2">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="AN147" t="s" s="2">
         <v>78</v>
@@ -20121,10 +20160,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>600</v>
+        <v>606</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20150,16 +20189,16 @@
         <v>103</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="O148" t="s" s="2">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>78</v>
@@ -20208,7 +20247,7 @@
         <v>78</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>79</v>
@@ -20226,10 +20265,10 @@
         <v>78</v>
       </c>
       <c r="AL148" t="s" s="2">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="AM148" t="s" s="2">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="AN148" t="s" s="2">
         <v>78</v>
@@ -20240,13 +20279,13 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>601</v>
+        <v>607</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="C149" t="s" s="2">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="D149" t="s" s="2">
         <v>78</v>
@@ -20268,19 +20307,19 @@
         <v>90</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="O149" t="s" s="2">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>78</v>
@@ -20305,11 +20344,11 @@
         <v>78</v>
       </c>
       <c r="X149" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="Y149" s="2"/>
       <c r="Z149" t="s" s="2">
-        <v>604</v>
+        <v>610</v>
       </c>
       <c r="AA149" t="s" s="2">
         <v>78</v>
@@ -20327,7 +20366,7 @@
         <v>78</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>79</v>
@@ -20342,27 +20381,27 @@
         <v>101</v>
       </c>
       <c r="AK149" t="s" s="2">
-        <v>78</v>
+        <v>611</v>
       </c>
       <c r="AL149" t="s" s="2">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="AM149" t="s" s="2">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="AN149" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AO149" t="s" s="2">
-        <v>528</v>
+        <v>534</v>
       </c>
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>605</v>
+        <v>612</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20474,10 +20513,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>606</v>
+        <v>613</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20589,13 +20628,13 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>607</v>
+        <v>614</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="D152" t="s" s="2">
         <v>78</v>
@@ -20617,13 +20656,13 @@
         <v>78</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -20706,10 +20745,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>608</v>
+        <v>615</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20821,10 +20860,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>609</v>
+        <v>616</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -20936,10 +20975,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>610</v>
+        <v>617</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -20979,7 +21018,7 @@
       </c>
       <c r="Q155" s="2"/>
       <c r="R155" t="s" s="2">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="S155" t="s" s="2">
         <v>78</v>
@@ -21053,10 +21092,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>611</v>
+        <v>618</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21097,7 +21136,7 @@
         <v>78</v>
       </c>
       <c r="S156" t="s" s="2">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="T156" t="s" s="2">
         <v>78</v>
@@ -21112,11 +21151,11 @@
         <v>78</v>
       </c>
       <c r="X156" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="Y156" s="2"/>
       <c r="Z156" t="s" s="2">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="AA156" t="s" s="2">
         <v>78</v>
@@ -21166,10 +21205,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>612</v>
+        <v>619</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21195,16 +21234,16 @@
         <v>153</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="O157" t="s" s="2">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>78</v>
@@ -21253,7 +21292,7 @@
         <v>78</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>79</v>
@@ -21271,10 +21310,10 @@
         <v>78</v>
       </c>
       <c r="AL157" t="s" s="2">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="AM157" t="s" s="2">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="AN157" t="s" s="2">
         <v>78</v>
@@ -21285,10 +21324,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>613</v>
+        <v>620</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21314,16 +21353,16 @@
         <v>103</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="O158" t="s" s="2">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>78</v>
@@ -21372,7 +21411,7 @@
         <v>78</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>79</v>
@@ -21390,10 +21429,10 @@
         <v>78</v>
       </c>
       <c r="AL158" t="s" s="2">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="AM158" t="s" s="2">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="AN158" t="s" s="2">
         <v>78</v>
@@ -21404,13 +21443,13 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>614</v>
+        <v>621</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="C159" t="s" s="2">
-        <v>615</v>
+        <v>622</v>
       </c>
       <c r="D159" t="s" s="2">
         <v>78</v>
@@ -21432,19 +21471,19 @@
         <v>90</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>616</v>
+        <v>623</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="O159" t="s" s="2">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>78</v>
@@ -21469,11 +21508,11 @@
         <v>78</v>
       </c>
       <c r="X159" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="Y159" s="2"/>
       <c r="Z159" t="s" s="2">
-        <v>617</v>
+        <v>624</v>
       </c>
       <c r="AA159" t="s" s="2">
         <v>78</v>
@@ -21491,7 +21530,7 @@
         <v>78</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>79</v>
@@ -21506,27 +21545,27 @@
         <v>101</v>
       </c>
       <c r="AK159" t="s" s="2">
-        <v>78</v>
+        <v>625</v>
       </c>
       <c r="AL159" t="s" s="2">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="AM159" t="s" s="2">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="AN159" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AO159" t="s" s="2">
-        <v>528</v>
+        <v>534</v>
       </c>
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21638,10 +21677,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -21753,13 +21792,13 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="C162" t="s" s="2">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="D162" t="s" s="2">
         <v>78</v>
@@ -21781,13 +21820,13 @@
         <v>78</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
@@ -21870,10 +21909,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>621</v>
+        <v>629</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -21985,10 +22024,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>622</v>
+        <v>630</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22100,10 +22139,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>623</v>
+        <v>631</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22143,7 +22182,7 @@
       </c>
       <c r="Q165" s="2"/>
       <c r="R165" t="s" s="2">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="S165" t="s" s="2">
         <v>78</v>
@@ -22217,10 +22256,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>624</v>
+        <v>632</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22261,7 +22300,7 @@
         <v>78</v>
       </c>
       <c r="S166" t="s" s="2">
-        <v>615</v>
+        <v>622</v>
       </c>
       <c r="T166" t="s" s="2">
         <v>78</v>
@@ -22276,11 +22315,11 @@
         <v>78</v>
       </c>
       <c r="X166" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="Y166" s="2"/>
       <c r="Z166" t="s" s="2">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="AA166" t="s" s="2">
         <v>78</v>
@@ -22330,10 +22369,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>625</v>
+        <v>633</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22359,16 +22398,16 @@
         <v>153</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="O167" t="s" s="2">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>78</v>
@@ -22417,7 +22456,7 @@
         <v>78</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>79</v>
@@ -22435,10 +22474,10 @@
         <v>78</v>
       </c>
       <c r="AL167" t="s" s="2">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="AM167" t="s" s="2">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="AN167" t="s" s="2">
         <v>78</v>
@@ -22449,10 +22488,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>626</v>
+        <v>634</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22478,16 +22517,16 @@
         <v>103</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="N168" t="s" s="2">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="O168" t="s" s="2">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>78</v>
@@ -22536,7 +22575,7 @@
         <v>78</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>79</v>
@@ -22554,10 +22593,10 @@
         <v>78</v>
       </c>
       <c r="AL168" t="s" s="2">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="AM168" t="s" s="2">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="AN168" t="s" s="2">
         <v>78</v>
@@ -22568,13 +22607,13 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="C169" t="s" s="2">
-        <v>628</v>
+        <v>636</v>
       </c>
       <c r="D169" t="s" s="2">
         <v>78</v>
@@ -22596,19 +22635,19 @@
         <v>90</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>629</v>
+        <v>637</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="O169" t="s" s="2">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>78</v>
@@ -22633,11 +22672,11 @@
         <v>78</v>
       </c>
       <c r="X169" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="Y169" s="2"/>
       <c r="Z169" t="s" s="2">
-        <v>630</v>
+        <v>638</v>
       </c>
       <c r="AA169" t="s" s="2">
         <v>78</v>
@@ -22655,7 +22694,7 @@
         <v>78</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>79</v>
@@ -22673,24 +22712,24 @@
         <v>78</v>
       </c>
       <c r="AL169" t="s" s="2">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="AM169" t="s" s="2">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="AN169" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AO169" t="s" s="2">
-        <v>528</v>
+        <v>534</v>
       </c>
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>631</v>
+        <v>639</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -22802,10 +22841,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>632</v>
+        <v>640</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -22917,13 +22956,13 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>633</v>
+        <v>641</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="C172" t="s" s="2">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="D172" t="s" s="2">
         <v>78</v>
@@ -22945,13 +22984,13 @@
         <v>78</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="N172" s="2"/>
       <c r="O172" s="2"/>
@@ -23034,10 +23073,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>634</v>
+        <v>642</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23149,10 +23188,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>635</v>
+        <v>643</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23264,10 +23303,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>636</v>
+        <v>644</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23307,7 +23346,7 @@
       </c>
       <c r="Q175" s="2"/>
       <c r="R175" t="s" s="2">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="S175" t="s" s="2">
         <v>78</v>
@@ -23381,10 +23420,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>637</v>
+        <v>645</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23425,7 +23464,7 @@
         <v>78</v>
       </c>
       <c r="S176" t="s" s="2">
-        <v>628</v>
+        <v>636</v>
       </c>
       <c r="T176" t="s" s="2">
         <v>78</v>
@@ -23440,11 +23479,11 @@
         <v>78</v>
       </c>
       <c r="X176" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="Y176" s="2"/>
       <c r="Z176" t="s" s="2">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="AA176" t="s" s="2">
         <v>78</v>
@@ -23494,10 +23533,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>638</v>
+        <v>646</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -23523,16 +23562,16 @@
         <v>153</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="O177" t="s" s="2">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="P177" t="s" s="2">
         <v>78</v>
@@ -23581,7 +23620,7 @@
         <v>78</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>79</v>
@@ -23599,10 +23638,10 @@
         <v>78</v>
       </c>
       <c r="AL177" t="s" s="2">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="AM177" t="s" s="2">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="AN177" t="s" s="2">
         <v>78</v>
@@ -23613,10 +23652,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>639</v>
+        <v>647</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -23642,16 +23681,16 @@
         <v>103</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="N178" t="s" s="2">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="O178" t="s" s="2">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="P178" t="s" s="2">
         <v>78</v>
@@ -23700,7 +23739,7 @@
         <v>78</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>79</v>
@@ -23718,10 +23757,10 @@
         <v>78</v>
       </c>
       <c r="AL178" t="s" s="2">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="AM178" t="s" s="2">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="AN178" t="s" s="2">
         <v>78</v>
@@ -23732,13 +23771,13 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>640</v>
+        <v>648</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="C179" t="s" s="2">
-        <v>641</v>
+        <v>649</v>
       </c>
       <c r="D179" t="s" s="2">
         <v>78</v>
@@ -23760,19 +23799,19 @@
         <v>90</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>642</v>
+        <v>650</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="N179" t="s" s="2">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="O179" t="s" s="2">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>78</v>
@@ -23800,28 +23839,28 @@
         <v>165</v>
       </c>
       <c r="Y179" t="s" s="2">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="Z179" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="AA179" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB179" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC179" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD179" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE179" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF179" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="AA179" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB179" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC179" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD179" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE179" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF179" t="s" s="2">
-        <v>518</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>79</v>
@@ -23839,24 +23878,24 @@
         <v>78</v>
       </c>
       <c r="AL179" t="s" s="2">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="AM179" t="s" s="2">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="AN179" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AO179" t="s" s="2">
-        <v>528</v>
+        <v>534</v>
       </c>
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>643</v>
+        <v>651</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -23968,10 +24007,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>644</v>
+        <v>652</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24083,13 +24122,13 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>645</v>
+        <v>653</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="C182" t="s" s="2">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="D182" t="s" s="2">
         <v>78</v>
@@ -24111,13 +24150,13 @@
         <v>78</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="N182" s="2"/>
       <c r="O182" s="2"/>
@@ -24200,10 +24239,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>646</v>
+        <v>654</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24315,10 +24354,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>647</v>
+        <v>655</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -24430,10 +24469,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>648</v>
+        <v>656</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -24473,7 +24512,7 @@
       </c>
       <c r="Q185" s="2"/>
       <c r="R185" t="s" s="2">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="S185" t="s" s="2">
         <v>78</v>
@@ -24547,10 +24586,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>649</v>
+        <v>657</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -24591,7 +24630,7 @@
         <v>78</v>
       </c>
       <c r="S186" t="s" s="2">
-        <v>641</v>
+        <v>649</v>
       </c>
       <c r="T186" t="s" s="2">
         <v>78</v>
@@ -24606,11 +24645,11 @@
         <v>78</v>
       </c>
       <c r="X186" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="Y186" s="2"/>
       <c r="Z186" t="s" s="2">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="AA186" t="s" s="2">
         <v>78</v>
@@ -24660,10 +24699,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>650</v>
+        <v>658</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -24689,16 +24728,16 @@
         <v>153</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="N187" t="s" s="2">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="O187" t="s" s="2">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="P187" t="s" s="2">
         <v>78</v>
@@ -24747,7 +24786,7 @@
         <v>78</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>79</v>
@@ -24765,10 +24804,10 @@
         <v>78</v>
       </c>
       <c r="AL187" t="s" s="2">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="AM187" t="s" s="2">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="AN187" t="s" s="2">
         <v>78</v>
@@ -24779,10 +24818,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>651</v>
+        <v>659</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -24808,16 +24847,16 @@
         <v>103</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="N188" t="s" s="2">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="O188" t="s" s="2">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="P188" t="s" s="2">
         <v>78</v>
@@ -24866,7 +24905,7 @@
         <v>78</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>79</v>
@@ -24884,10 +24923,10 @@
         <v>78</v>
       </c>
       <c r="AL188" t="s" s="2">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="AM188" t="s" s="2">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="AN188" t="s" s="2">
         <v>78</v>
@@ -24898,10 +24937,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>652</v>
+        <v>660</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>652</v>
+        <v>660</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -24927,16 +24966,16 @@
         <v>103</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>653</v>
+        <v>661</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>654</v>
+        <v>662</v>
       </c>
       <c r="N189" t="s" s="2">
-        <v>655</v>
+        <v>663</v>
       </c>
       <c r="O189" t="s" s="2">
-        <v>656</v>
+        <v>664</v>
       </c>
       <c r="P189" t="s" s="2">
         <v>78</v>
@@ -24985,7 +25024,7 @@
         <v>78</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>652</v>
+        <v>660</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>79</v>
@@ -24994,22 +25033,22 @@
         <v>89</v>
       </c>
       <c r="AI189" t="s" s="2">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="AJ189" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK189" t="s" s="2">
-        <v>78</v>
+        <v>665</v>
       </c>
       <c r="AL189" t="s" s="2">
-        <v>657</v>
+        <v>666</v>
       </c>
       <c r="AM189" t="s" s="2">
-        <v>658</v>
+        <v>667</v>
       </c>
       <c r="AN189" t="s" s="2">
-        <v>659</v>
+        <v>668</v>
       </c>
       <c r="AO189" t="s" s="2">
         <v>78</v>
@@ -25017,10 +25056,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>660</v>
+        <v>669</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>660</v>
+        <v>669</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -25046,16 +25085,16 @@
         <v>103</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>661</v>
+        <v>670</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>662</v>
+        <v>671</v>
       </c>
       <c r="N190" t="s" s="2">
-        <v>663</v>
+        <v>672</v>
       </c>
       <c r="O190" t="s" s="2">
-        <v>664</v>
+        <v>673</v>
       </c>
       <c r="P190" t="s" s="2">
         <v>78</v>
@@ -25104,7 +25143,7 @@
         <v>78</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>660</v>
+        <v>669</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>79</v>
@@ -25119,13 +25158,13 @@
         <v>101</v>
       </c>
       <c r="AK190" t="s" s="2">
-        <v>78</v>
+        <v>674</v>
       </c>
       <c r="AL190" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM190" t="s" s="2">
-        <v>658</v>
+        <v>667</v>
       </c>
       <c r="AN190" t="s" s="2">
         <v>78</v>
@@ -25136,10 +25175,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>665</v>
+        <v>675</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>665</v>
+        <v>675</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -25162,19 +25201,19 @@
         <v>78</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>666</v>
+        <v>676</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>667</v>
+        <v>677</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>668</v>
+        <v>678</v>
       </c>
       <c r="N191" t="s" s="2">
-        <v>669</v>
+        <v>679</v>
       </c>
       <c r="O191" t="s" s="2">
-        <v>670</v>
+        <v>680</v>
       </c>
       <c r="P191" t="s" s="2">
         <v>78</v>
@@ -25211,7 +25250,7 @@
         <v>78</v>
       </c>
       <c r="AB191" t="s" s="2">
-        <v>671</v>
+        <v>681</v>
       </c>
       <c r="AC191" s="2"/>
       <c r="AD191" t="s" s="2">
@@ -25221,7 +25260,7 @@
         <v>116</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>665</v>
+        <v>675</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>79</v>
@@ -25233,19 +25272,19 @@
         <v>207</v>
       </c>
       <c r="AJ191" t="s" s="2">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="AK191" t="s" s="2">
-        <v>78</v>
+        <v>683</v>
       </c>
       <c r="AL191" t="s" s="2">
-        <v>673</v>
+        <v>684</v>
       </c>
       <c r="AM191" t="s" s="2">
-        <v>674</v>
+        <v>685</v>
       </c>
       <c r="AN191" t="s" s="2">
-        <v>675</v>
+        <v>686</v>
       </c>
       <c r="AO191" t="s" s="2">
         <v>78</v>
@@ -25253,10 +25292,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>676</v>
+        <v>687</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>676</v>
+        <v>687</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -25368,10 +25407,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>677</v>
+        <v>688</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>677</v>
+        <v>688</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -25485,13 +25524,13 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>678</v>
+        <v>689</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>677</v>
+        <v>688</v>
       </c>
       <c r="C194" t="s" s="2">
-        <v>679</v>
+        <v>690</v>
       </c>
       <c r="D194" t="s" s="2">
         <v>78</v>
@@ -25513,13 +25552,13 @@
         <v>78</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>680</v>
+        <v>691</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>681</v>
+        <v>692</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>682</v>
+        <v>693</v>
       </c>
       <c r="N194" s="2"/>
       <c r="O194" s="2"/>
@@ -25602,10 +25641,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>683</v>
+        <v>694</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>683</v>
+        <v>694</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -25631,10 +25670,10 @@
         <v>175</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>684</v>
+        <v>695</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>685</v>
+        <v>696</v>
       </c>
       <c r="N195" s="2"/>
       <c r="O195" s="2"/>
@@ -25661,13 +25700,13 @@
         <v>78</v>
       </c>
       <c r="X195" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="Y195" t="s" s="2">
-        <v>686</v>
+        <v>697</v>
       </c>
       <c r="Z195" t="s" s="2">
-        <v>687</v>
+        <v>698</v>
       </c>
       <c r="AA195" t="s" s="2">
         <v>78</v>
@@ -25685,7 +25724,7 @@
         <v>78</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>688</v>
+        <v>699</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>79</v>
@@ -25694,7 +25733,7 @@
         <v>89</v>
       </c>
       <c r="AI195" t="s" s="2">
-        <v>689</v>
+        <v>700</v>
       </c>
       <c r="AJ195" t="s" s="2">
         <v>101</v>
@@ -25703,13 +25742,13 @@
         <v>78</v>
       </c>
       <c r="AL195" t="s" s="2">
-        <v>690</v>
+        <v>701</v>
       </c>
       <c r="AM195" t="s" s="2">
-        <v>691</v>
+        <v>702</v>
       </c>
       <c r="AN195" t="s" s="2">
-        <v>692</v>
+        <v>703</v>
       </c>
       <c r="AO195" t="s" s="2">
         <v>78</v>
@@ -25717,10 +25756,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>693</v>
+        <v>704</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>693</v>
+        <v>704</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -25746,16 +25785,16 @@
         <v>103</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>694</v>
+        <v>705</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>695</v>
+        <v>706</v>
       </c>
       <c r="N196" t="s" s="2">
-        <v>696</v>
+        <v>707</v>
       </c>
       <c r="O196" t="s" s="2">
-        <v>697</v>
+        <v>708</v>
       </c>
       <c r="P196" t="s" s="2">
         <v>78</v>
@@ -25804,7 +25843,7 @@
         <v>78</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>698</v>
+        <v>709</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>79</v>
@@ -25822,13 +25861,13 @@
         <v>78</v>
       </c>
       <c r="AL196" t="s" s="2">
-        <v>699</v>
+        <v>710</v>
       </c>
       <c r="AM196" t="s" s="2">
-        <v>700</v>
+        <v>711</v>
       </c>
       <c r="AN196" t="s" s="2">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="AO196" t="s" s="2">
         <v>78</v>
@@ -25836,10 +25875,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>701</v>
+        <v>712</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>701</v>
+        <v>712</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -25865,16 +25904,16 @@
         <v>175</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>702</v>
+        <v>713</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>703</v>
+        <v>714</v>
       </c>
       <c r="N197" t="s" s="2">
-        <v>704</v>
+        <v>715</v>
       </c>
       <c r="O197" t="s" s="2">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="P197" t="s" s="2">
         <v>78</v>
@@ -25899,13 +25938,13 @@
         <v>78</v>
       </c>
       <c r="X197" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="Y197" t="s" s="2">
-        <v>706</v>
+        <v>717</v>
       </c>
       <c r="Z197" t="s" s="2">
-        <v>707</v>
+        <v>718</v>
       </c>
       <c r="AA197" t="s" s="2">
         <v>78</v>
@@ -25923,7 +25962,7 @@
         <v>78</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>708</v>
+        <v>719</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>79</v>
@@ -25941,13 +25980,13 @@
         <v>78</v>
       </c>
       <c r="AL197" t="s" s="2">
-        <v>709</v>
+        <v>720</v>
       </c>
       <c r="AM197" t="s" s="2">
-        <v>710</v>
+        <v>721</v>
       </c>
       <c r="AN197" t="s" s="2">
-        <v>711</v>
+        <v>722</v>
       </c>
       <c r="AO197" t="s" s="2">
         <v>78</v>
@@ -25955,10 +25994,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>712</v>
+        <v>723</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>712</v>
+        <v>723</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -25981,16 +26020,16 @@
         <v>90</v>
       </c>
       <c r="K198" t="s" s="2">
-        <v>713</v>
+        <v>724</v>
       </c>
       <c r="L198" t="s" s="2">
-        <v>714</v>
+        <v>725</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>715</v>
+        <v>726</v>
       </c>
       <c r="N198" t="s" s="2">
-        <v>716</v>
+        <v>727</v>
       </c>
       <c r="O198" s="2"/>
       <c r="P198" t="s" s="2">
@@ -26040,7 +26079,7 @@
         <v>78</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>717</v>
+        <v>728</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>79</v>
@@ -26072,10 +26111,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>718</v>
+        <v>729</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>718</v>
+        <v>729</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -26101,10 +26140,10 @@
         <v>230</v>
       </c>
       <c r="L199" t="s" s="2">
-        <v>719</v>
+        <v>730</v>
       </c>
       <c r="M199" t="s" s="2">
-        <v>720</v>
+        <v>731</v>
       </c>
       <c r="N199" s="2"/>
       <c r="O199" s="2"/>
@@ -26155,7 +26194,7 @@
         <v>78</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>721</v>
+        <v>732</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>79</v>
@@ -26176,10 +26215,10 @@
         <v>198</v>
       </c>
       <c r="AM199" t="s" s="2">
-        <v>722</v>
+        <v>733</v>
       </c>
       <c r="AN199" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="AO199" t="s" s="2">
         <v>78</v>
@@ -26187,13 +26226,13 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>723</v>
+        <v>734</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>665</v>
+        <v>675</v>
       </c>
       <c r="C200" t="s" s="2">
-        <v>724</v>
+        <v>735</v>
       </c>
       <c r="D200" t="s" s="2">
         <v>78</v>
@@ -26215,19 +26254,19 @@
         <v>78</v>
       </c>
       <c r="K200" t="s" s="2">
-        <v>725</v>
+        <v>736</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>726</v>
+        <v>737</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>668</v>
+        <v>678</v>
       </c>
       <c r="N200" t="s" s="2">
-        <v>669</v>
+        <v>679</v>
       </c>
       <c r="O200" t="s" s="2">
-        <v>670</v>
+        <v>680</v>
       </c>
       <c r="P200" t="s" s="2">
         <v>78</v>
@@ -26276,7 +26315,7 @@
         <v>78</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>665</v>
+        <v>675</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>79</v>
@@ -26288,19 +26327,19 @@
         <v>207</v>
       </c>
       <c r="AJ200" t="s" s="2">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="AK200" t="s" s="2">
-        <v>78</v>
+        <v>738</v>
       </c>
       <c r="AL200" t="s" s="2">
-        <v>673</v>
+        <v>684</v>
       </c>
       <c r="AM200" t="s" s="2">
-        <v>674</v>
+        <v>685</v>
       </c>
       <c r="AN200" t="s" s="2">
-        <v>675</v>
+        <v>686</v>
       </c>
       <c r="AO200" t="s" s="2">
         <v>78</v>
@@ -26308,10 +26347,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>727</v>
+        <v>739</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>727</v>
+        <v>739</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -26334,19 +26373,19 @@
         <v>78</v>
       </c>
       <c r="K201" t="s" s="2">
-        <v>728</v>
+        <v>740</v>
       </c>
       <c r="L201" t="s" s="2">
-        <v>729</v>
+        <v>741</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>730</v>
+        <v>742</v>
       </c>
       <c r="N201" t="s" s="2">
-        <v>731</v>
+        <v>743</v>
       </c>
       <c r="O201" t="s" s="2">
-        <v>732</v>
+        <v>744</v>
       </c>
       <c r="P201" t="s" s="2">
         <v>78</v>
@@ -26395,7 +26434,7 @@
         <v>78</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>727</v>
+        <v>739</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>79</v>
@@ -26407,19 +26446,19 @@
         <v>207</v>
       </c>
       <c r="AJ201" t="s" s="2">
-        <v>733</v>
+        <v>745</v>
       </c>
       <c r="AK201" t="s" s="2">
-        <v>78</v>
+        <v>746</v>
       </c>
       <c r="AL201" t="s" s="2">
-        <v>734</v>
+        <v>747</v>
       </c>
       <c r="AM201" t="s" s="2">
-        <v>735</v>
+        <v>748</v>
       </c>
       <c r="AN201" t="s" s="2">
-        <v>736</v>
+        <v>749</v>
       </c>
       <c r="AO201" t="s" s="2">
         <v>78</v>
@@ -26427,10 +26466,10 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>737</v>
+        <v>750</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>737</v>
+        <v>750</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -26453,17 +26492,17 @@
         <v>90</v>
       </c>
       <c r="K202" t="s" s="2">
-        <v>738</v>
+        <v>751</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>739</v>
+        <v>752</v>
       </c>
       <c r="M202" t="s" s="2">
-        <v>740</v>
+        <v>753</v>
       </c>
       <c r="N202" s="2"/>
       <c r="O202" t="s" s="2">
-        <v>741</v>
+        <v>754</v>
       </c>
       <c r="P202" t="s" s="2">
         <v>78</v>
@@ -26512,7 +26551,7 @@
         <v>78</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>737</v>
+        <v>750</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>79</v>
@@ -26530,10 +26569,10 @@
         <v>78</v>
       </c>
       <c r="AL202" t="s" s="2">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="AM202" t="s" s="2">
-        <v>742</v>
+        <v>755</v>
       </c>
       <c r="AN202" t="s" s="2">
         <v>107</v>
@@ -26544,10 +26583,10 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>743</v>
+        <v>756</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>743</v>
+        <v>756</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -26659,10 +26698,10 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>744</v>
+        <v>757</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>744</v>
+        <v>757</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -26776,10 +26815,10 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>745</v>
+        <v>758</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>745</v>
+        <v>758</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -26805,13 +26844,13 @@
         <v>103</v>
       </c>
       <c r="L205" t="s" s="2">
-        <v>746</v>
+        <v>759</v>
       </c>
       <c r="M205" t="s" s="2">
-        <v>747</v>
+        <v>760</v>
       </c>
       <c r="N205" t="s" s="2">
-        <v>748</v>
+        <v>761</v>
       </c>
       <c r="O205" s="2"/>
       <c r="P205" t="s" s="2">
@@ -26861,7 +26900,7 @@
         <v>78</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>749</v>
+        <v>762</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>79</v>
@@ -26870,7 +26909,7 @@
         <v>89</v>
       </c>
       <c r="AI205" t="s" s="2">
-        <v>750</v>
+        <v>763</v>
       </c>
       <c r="AJ205" t="s" s="2">
         <v>101</v>
@@ -26893,10 +26932,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>751</v>
+        <v>764</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>751</v>
+        <v>764</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -26922,13 +26961,13 @@
         <v>136</v>
       </c>
       <c r="L206" t="s" s="2">
-        <v>752</v>
+        <v>765</v>
       </c>
       <c r="M206" t="s" s="2">
-        <v>753</v>
+        <v>766</v>
       </c>
       <c r="N206" t="s" s="2">
-        <v>754</v>
+        <v>767</v>
       </c>
       <c r="O206" s="2"/>
       <c r="P206" t="s" s="2">
@@ -26958,7 +26997,7 @@
       </c>
       <c r="Y206" s="2"/>
       <c r="Z206" t="s" s="2">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="AA206" t="s" s="2">
         <v>78</v>
@@ -26976,7 +27015,7 @@
         <v>78</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>755</v>
+        <v>768</v>
       </c>
       <c r="AG206" t="s" s="2">
         <v>79</v>
@@ -27008,10 +27047,10 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>756</v>
+        <v>769</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>756</v>
+        <v>769</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -27034,16 +27073,16 @@
         <v>90</v>
       </c>
       <c r="K207" t="s" s="2">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="L207" t="s" s="2">
-        <v>757</v>
+        <v>770</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>758</v>
+        <v>771</v>
       </c>
       <c r="N207" t="s" s="2">
-        <v>759</v>
+        <v>772</v>
       </c>
       <c r="O207" s="2"/>
       <c r="P207" t="s" s="2">
@@ -27093,7 +27132,7 @@
         <v>78</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>760</v>
+        <v>773</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>79</v>
@@ -27114,7 +27153,7 @@
         <v>78</v>
       </c>
       <c r="AM207" t="s" s="2">
-        <v>761</v>
+        <v>774</v>
       </c>
       <c r="AN207" t="s" s="2">
         <v>78</v>
@@ -27125,10 +27164,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>762</v>
+        <v>775</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>762</v>
+        <v>775</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -27154,13 +27193,13 @@
         <v>103</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>763</v>
+        <v>776</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>764</v>
+        <v>777</v>
       </c>
       <c r="N208" t="s" s="2">
-        <v>765</v>
+        <v>778</v>
       </c>
       <c r="O208" s="2"/>
       <c r="P208" t="s" s="2">
@@ -27210,7 +27249,7 @@
         <v>78</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>766</v>
+        <v>779</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>79</v>
@@ -27242,10 +27281,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>767</v>
+        <v>780</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>767</v>
+        <v>780</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -27268,19 +27307,19 @@
         <v>78</v>
       </c>
       <c r="K209" t="s" s="2">
-        <v>768</v>
+        <v>781</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>769</v>
+        <v>782</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>770</v>
+        <v>783</v>
       </c>
       <c r="N209" t="s" s="2">
-        <v>771</v>
+        <v>784</v>
       </c>
       <c r="O209" t="s" s="2">
-        <v>772</v>
+        <v>785</v>
       </c>
       <c r="P209" t="s" s="2">
         <v>78</v>
@@ -27329,7 +27368,7 @@
         <v>78</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>767</v>
+        <v>780</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>79</v>
@@ -27350,7 +27389,7 @@
         <v>78</v>
       </c>
       <c r="AM209" t="s" s="2">
-        <v>773</v>
+        <v>786</v>
       </c>
       <c r="AN209" t="s" s="2">
         <v>78</v>
@@ -27361,10 +27400,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>774</v>
+        <v>787</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>774</v>
+        <v>787</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -27476,10 +27515,10 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>775</v>
+        <v>788</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>775</v>
+        <v>788</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -27593,14 +27632,14 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>776</v>
+        <v>789</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>776</v>
+        <v>789</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
-        <v>777</v>
+        <v>790</v>
       </c>
       <c r="E212" s="2"/>
       <c r="F212" t="s" s="2">
@@ -27622,16 +27661,16 @@
         <v>110</v>
       </c>
       <c r="L212" t="s" s="2">
-        <v>778</v>
+        <v>791</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>779</v>
+        <v>792</v>
       </c>
       <c r="N212" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O212" t="s" s="2">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="P212" t="s" s="2">
         <v>78</v>
@@ -27680,7 +27719,7 @@
         <v>78</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>780</v>
+        <v>793</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>79</v>
@@ -27712,10 +27751,10 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>781</v>
+        <v>794</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>781</v>
+        <v>794</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -27738,17 +27777,17 @@
         <v>78</v>
       </c>
       <c r="K213" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>782</v>
+        <v>795</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>783</v>
+        <v>796</v>
       </c>
       <c r="N213" s="2"/>
       <c r="O213" t="s" s="2">
-        <v>784</v>
+        <v>797</v>
       </c>
       <c r="P213" t="s" s="2">
         <v>78</v>
@@ -27776,10 +27815,10 @@
         <v>157</v>
       </c>
       <c r="Y213" t="s" s="2">
-        <v>785</v>
+        <v>798</v>
       </c>
       <c r="Z213" t="s" s="2">
-        <v>786</v>
+        <v>799</v>
       </c>
       <c r="AA213" t="s" s="2">
         <v>78</v>
@@ -27797,7 +27836,7 @@
         <v>78</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>781</v>
+        <v>794</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>79</v>
@@ -27818,7 +27857,7 @@
         <v>78</v>
       </c>
       <c r="AM213" t="s" s="2">
-        <v>787</v>
+        <v>800</v>
       </c>
       <c r="AN213" t="s" s="2">
         <v>78</v>
@@ -27829,10 +27868,10 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>788</v>
+        <v>801</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>788</v>
+        <v>801</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -27855,17 +27894,17 @@
         <v>78</v>
       </c>
       <c r="K214" t="s" s="2">
-        <v>789</v>
+        <v>802</v>
       </c>
       <c r="L214" t="s" s="2">
-        <v>790</v>
+        <v>803</v>
       </c>
       <c r="M214" t="s" s="2">
-        <v>791</v>
+        <v>804</v>
       </c>
       <c r="N214" s="2"/>
       <c r="O214" t="s" s="2">
-        <v>792</v>
+        <v>805</v>
       </c>
       <c r="P214" t="s" s="2">
         <v>78</v>
@@ -27914,7 +27953,7 @@
         <v>78</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>788</v>
+        <v>801</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>79</v>
@@ -27932,10 +27971,10 @@
         <v>78</v>
       </c>
       <c r="AL214" t="s" s="2">
-        <v>793</v>
+        <v>806</v>
       </c>
       <c r="AM214" t="s" s="2">
-        <v>794</v>
+        <v>807</v>
       </c>
       <c r="AN214" t="s" s="2">
         <v>78</v>
@@ -27946,10 +27985,10 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>795</v>
+        <v>808</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>795</v>
+        <v>808</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -27972,17 +28011,17 @@
         <v>78</v>
       </c>
       <c r="K215" t="s" s="2">
-        <v>666</v>
+        <v>676</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>796</v>
+        <v>809</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>668</v>
+        <v>678</v>
       </c>
       <c r="N215" s="2"/>
       <c r="O215" t="s" s="2">
-        <v>797</v>
+        <v>810</v>
       </c>
       <c r="P215" t="s" s="2">
         <v>78</v>
@@ -28031,7 +28070,7 @@
         <v>78</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>795</v>
+        <v>808</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>79</v>
@@ -28043,19 +28082,19 @@
         <v>207</v>
       </c>
       <c r="AJ215" t="s" s="2">
-        <v>798</v>
+        <v>811</v>
       </c>
       <c r="AK215" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL215" t="s" s="2">
-        <v>673</v>
+        <v>684</v>
       </c>
       <c r="AM215" t="s" s="2">
-        <v>674</v>
+        <v>685</v>
       </c>
       <c r="AN215" t="s" s="2">
-        <v>675</v>
+        <v>686</v>
       </c>
       <c r="AO215" t="s" s="2">
         <v>78</v>
@@ -28063,10 +28102,10 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>799</v>
+        <v>812</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>799</v>
+        <v>812</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -28089,19 +28128,19 @@
         <v>78</v>
       </c>
       <c r="K216" t="s" s="2">
-        <v>800</v>
+        <v>813</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>801</v>
+        <v>814</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>730</v>
+        <v>742</v>
       </c>
       <c r="N216" t="s" s="2">
-        <v>731</v>
+        <v>743</v>
       </c>
       <c r="O216" t="s" s="2">
-        <v>802</v>
+        <v>815</v>
       </c>
       <c r="P216" t="s" s="2">
         <v>78</v>
@@ -28150,7 +28189,7 @@
         <v>78</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>799</v>
+        <v>812</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>79</v>
@@ -28168,13 +28207,13 @@
         <v>78</v>
       </c>
       <c r="AL216" t="s" s="2">
-        <v>734</v>
+        <v>747</v>
       </c>
       <c r="AM216" t="s" s="2">
-        <v>735</v>
+        <v>748</v>
       </c>
       <c r="AN216" t="s" s="2">
-        <v>736</v>
+        <v>749</v>
       </c>
       <c r="AO216" t="s" s="2">
         <v>78</v>
@@ -28182,10 +28221,10 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>803</v>
+        <v>816</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>803</v>
+        <v>816</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -28208,17 +28247,17 @@
         <v>78</v>
       </c>
       <c r="K217" t="s" s="2">
-        <v>804</v>
+        <v>817</v>
       </c>
       <c r="L217" t="s" s="2">
-        <v>805</v>
+        <v>818</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>806</v>
+        <v>819</v>
       </c>
       <c r="N217" s="2"/>
       <c r="O217" t="s" s="2">
-        <v>807</v>
+        <v>820</v>
       </c>
       <c r="P217" t="s" s="2">
         <v>78</v>
@@ -28267,7 +28306,7 @@
         <v>78</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>803</v>
+        <v>816</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>79</v>

--- a/nr-add-mapping/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-dr-organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0-ballot-3</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T14:54:13+00:00</t>
+    <t>2024-04-08T13:06:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris (https://esante.gouv.fr, monserviceclient.annuaire@esante.gouv.fr)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/nr-add-mapping/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-08T13:06:58+00:00</t>
+    <t>2024-04-08T13:14:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-mapping/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-08T13:14:28+00:00</t>
+    <t>2024-04-08T13:35:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-mapping/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-dr-organization.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8295" uniqueCount="831">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8294" uniqueCount="831">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-08T13:35:38+00:00</t>
+    <t>2024-04-08T14:07:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -695,9 +695,6 @@
 </t>
   </si>
   <si>
-    <t>Optional Extensions Element</t>
-  </si>
-  <si>
     <t>The date range that this organization should be considered available.</t>
   </si>
   <si>
@@ -747,7 +744,7 @@
     <t>Value of extension</t>
   </si>
   <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/extensibility.html) for a list).</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -787,8 +784,8 @@
     <t>Period.start</t>
   </si>
   <si>
-    <t>ele-1
-per-1</t>
+    <t xml:space="preserve">per-1
+</t>
   </si>
   <si>
     <t>dateCreation</t>
@@ -1764,6 +1761,9 @@
   </si>
   <si>
     <t>Organization.type.extension.value[x]</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
     <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/ValueSet/as-vs-organization-types</t>
@@ -5507,10 +5507,10 @@
         <v>216</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -5585,7 +5585,7 @@
         <v>79</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>200</v>
+        <v>79</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>79</v>
@@ -5596,10 +5596,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="B23" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5714,14 +5714,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="B24" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="B24" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -5743,14 +5743,12 @@
         <v>112</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>113</v>
+        <v>202</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>115</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>79</v>
@@ -5808,7 +5806,7 @@
         <v>81</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>209</v>
+        <v>79</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>120</v>
@@ -5823,7 +5821,7 @@
         <v>79</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>200</v>
+        <v>79</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>79</v>
@@ -5834,10 +5832,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="B25" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="B25" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5863,13 +5861,13 @@
         <v>138</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5877,49 +5875,49 @@
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="S25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="S25" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T25" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U25" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V25" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W25" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X25" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y25" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z25" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>229</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>91</v>
@@ -5954,10 +5952,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="B26" t="s" s="2">
         <v>230</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>231</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5980,13 +5978,13 @@
         <v>79</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>234</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -6037,7 +6035,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -6046,7 +6044,7 @@
         <v>91</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>209</v>
+        <v>79</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>103</v>
@@ -6072,10 +6070,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="B27" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -6190,10 +6188,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="B28" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="B28" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -6284,7 +6282,7 @@
         <v>81</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>209</v>
+        <v>79</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>120</v>
@@ -6299,7 +6297,7 @@
         <v>79</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>200</v>
+        <v>109</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>79</v>
@@ -6310,10 +6308,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="B29" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6336,16 +6334,16 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>245</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -6395,31 +6393,31 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI29" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="AG29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH29" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI29" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AL29" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="AL29" t="s" s="2">
+      <c r="AM29" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="AM29" t="s" s="2">
+      <c r="AN29" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>251</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>79</v>
@@ -6430,10 +6428,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="B30" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="B30" t="s" s="2">
-        <v>253</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6456,69 +6454,69 @@
         <v>92</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q30" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="R30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF30" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="R30" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S30" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T30" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U30" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V30" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W30" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X30" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y30" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z30" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA30" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB30" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD30" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE30" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF30" t="s" s="2">
-        <v>258</v>
-      </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
@@ -6526,22 +6524,22 @@
         <v>91</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AM30" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="AL30" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="AM30" t="s" s="2">
+      <c r="AN30" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>79</v>
@@ -6552,13 +6550,13 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>201</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s" s="2">
         <v>79</v>
@@ -6580,13 +6578,13 @@
         <v>79</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -6672,13 +6670,13 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>201</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D32" t="s" s="2">
         <v>79</v>
@@ -6700,13 +6698,13 @@
         <v>79</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6772,7 +6770,7 @@
         <v>120</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>79</v>
@@ -6792,13 +6790,13 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>201</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D33" t="s" s="2">
         <v>79</v>
@@ -6820,13 +6818,13 @@
         <v>79</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>277</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6895,7 +6893,7 @@
         <v>79</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>79</v>
@@ -6912,13 +6910,13 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>201</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>79</v>
@@ -6940,13 +6938,13 @@
         <v>79</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -7012,10 +7010,10 @@
         <v>120</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>79</v>
@@ -7032,13 +7030,13 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>201</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D35" t="s" s="2">
         <v>79</v>
@@ -7060,13 +7058,13 @@
         <v>79</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>289</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -7135,7 +7133,7 @@
         <v>79</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>79</v>
@@ -7152,13 +7150,13 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>201</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D36" t="s" s="2">
         <v>79</v>
@@ -7180,13 +7178,13 @@
         <v>79</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -7272,10 +7270,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7301,16 +7299,16 @@
         <v>112</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="N37" t="s" s="2">
         <v>115</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>79</v>
@@ -7359,7 +7357,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -7394,10 +7392,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7420,17 +7418,17 @@
         <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>79</v>
@@ -7467,10 +7465,10 @@
         <v>79</v>
       </c>
       <c r="AB38" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AC38" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="AC38" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>79</v>
@@ -7479,7 +7477,7 @@
         <v>118</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -7488,7 +7486,7 @@
         <v>81</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>103</v>
@@ -7500,27 +7498,27 @@
         <v>79</v>
       </c>
       <c r="AM38" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AN38" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="AN38" t="s" s="2">
+      <c r="AO38" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="AO38" t="s" s="2">
+      <c r="AP38" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="AP38" t="s" s="2">
-        <v>312</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="C39" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="B39" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="C39" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>79</v>
@@ -7542,17 +7540,17 @@
         <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>79</v>
@@ -7601,7 +7599,7 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -7610,36 +7608,36 @@
         <v>81</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AM39" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AN39" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="AN39" t="s" s="2">
+      <c r="AO39" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="AO39" t="s" s="2">
+      <c r="AP39" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="AP39" t="s" s="2">
-        <v>312</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="B40" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="B40" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7754,10 +7752,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="B41" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="B41" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7874,10 +7872,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="B42" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="B42" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7903,16 +7901,16 @@
         <v>177</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="N42" t="s" s="2">
+      <c r="O42" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>79</v>
@@ -7922,46 +7920,46 @@
         <v>79</v>
       </c>
       <c r="S42" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="T42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X42" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="T42" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U42" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V42" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W42" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X42" t="s" s="2">
+      <c r="Y42" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="Y42" t="s" s="2">
+      <c r="Z42" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="Z42" t="s" s="2">
+      <c r="AA42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF42" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="AA42" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB42" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD42" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE42" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF42" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7985,7 +7983,7 @@
         <v>200</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>79</v>
@@ -7996,10 +7994,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="B43" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="B43" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -8022,19 +8020,19 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="N43" t="s" s="2">
+      <c r="O43" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>79</v>
@@ -8044,7 +8042,7 @@
         <v>79</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>79</v>
@@ -8062,28 +8060,28 @@
         <v>159</v>
       </c>
       <c r="Y43" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="Z43" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="Z43" t="s" s="2">
+      <c r="AA43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF43" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="AA43" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF43" t="s" s="2">
-        <v>343</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -8104,10 +8102,10 @@
         <v>79</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>79</v>
@@ -8118,10 +8116,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="B44" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="B44" t="s" s="2">
-        <v>346</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8147,16 +8145,16 @@
         <v>138</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="N44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>79</v>
@@ -8166,46 +8164,46 @@
         <v>79</v>
       </c>
       <c r="S44" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="T44" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="T44" t="s" s="2">
+      <c r="U44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF44" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="U44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -8226,13 +8224,13 @@
         <v>79</v>
       </c>
       <c r="AM44" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="AN44" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="AN44" t="s" s="2">
+      <c r="AO44" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="AO44" t="s" s="2">
-        <v>356</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>79</v>
@@ -8240,10 +8238,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="B45" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="B45" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8269,13 +8267,13 @@
         <v>105</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -8289,43 +8287,43 @@
         <v>79</v>
       </c>
       <c r="T45" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF45" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="U45" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V45" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W45" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X45" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y45" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z45" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA45" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB45" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD45" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE45" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF45" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -8346,13 +8344,13 @@
         <v>79</v>
       </c>
       <c r="AM45" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AN45" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="AN45" t="s" s="2">
+      <c r="AO45" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="AO45" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>79</v>
@@ -8360,10 +8358,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="B46" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8386,13 +8384,13 @@
         <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -8443,7 +8441,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -8464,13 +8462,13 @@
         <v>79</v>
       </c>
       <c r="AM46" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AN46" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AN46" t="s" s="2">
+      <c r="AO46" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="AO46" t="s" s="2">
-        <v>374</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>79</v>
@@ -8478,10 +8476,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="B47" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="B47" t="s" s="2">
-        <v>376</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8504,16 +8502,16 @@
         <v>92</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8563,7 +8561,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -8584,13 +8582,13 @@
         <v>79</v>
       </c>
       <c r="AM47" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AN47" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="AN47" t="s" s="2">
+      <c r="AO47" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>79</v>
@@ -8598,13 +8596,13 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="C48" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="B48" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="C48" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>79</v>
@@ -8626,17 +8624,17 @@
         <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>79</v>
@@ -8685,7 +8683,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8694,36 +8692,36 @@
         <v>81</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AM48" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AN48" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="AN48" t="s" s="2">
+      <c r="AO48" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="AO48" t="s" s="2">
+      <c r="AP48" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="AP48" t="s" s="2">
-        <v>312</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8838,10 +8836,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8958,10 +8956,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8987,16 +8985,16 @@
         <v>177</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="N51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>79</v>
@@ -9021,31 +9019,31 @@
         <v>79</v>
       </c>
       <c r="X51" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="Y51" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="Y51" t="s" s="2">
+      <c r="Z51" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="Z51" t="s" s="2">
+      <c r="AA51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF51" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="AA51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -9069,7 +9067,7 @@
         <v>200</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>79</v>
@@ -9080,10 +9078,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9106,19 +9104,19 @@
         <v>92</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="N52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>79</v>
@@ -9146,28 +9144,28 @@
         <v>159</v>
       </c>
       <c r="Y52" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="Z52" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="Z52" t="s" s="2">
+      <c r="AA52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF52" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>343</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -9188,10 +9186,10 @@
         <v>79</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>79</v>
@@ -9202,10 +9200,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="B53" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9320,10 +9318,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="B54" t="s" s="2">
         <v>395</v>
-      </c>
-      <c r="B54" t="s" s="2">
-        <v>396</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9440,10 +9438,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="B55" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="B55" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9469,16 +9467,16 @@
         <v>155</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="N55" t="s" s="2">
+      <c r="O55" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>79</v>
@@ -9527,7 +9525,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -9548,10 +9546,10 @@
         <v>79</v>
       </c>
       <c r="AM55" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AN55" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>79</v>
@@ -9562,10 +9560,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="B56" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="B56" t="s" s="2">
-        <v>407</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9680,10 +9678,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="B57" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="B57" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9800,10 +9798,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="B58" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="B58" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9829,16 +9827,16 @@
         <v>138</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="N58" t="s" s="2">
+      <c r="O58" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>79</v>
@@ -9848,46 +9846,46 @@
         <v>79</v>
       </c>
       <c r="S58" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF58" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="T58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF58" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9908,10 +9906,10 @@
         <v>79</v>
       </c>
       <c r="AM58" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AN58" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>79</v>
@@ -9922,10 +9920,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="B59" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>421</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9951,13 +9949,13 @@
         <v>105</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>424</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -10007,7 +10005,7 @@
         <v>79</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -10028,10 +10026,10 @@
         <v>79</v>
       </c>
       <c r="AM59" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AN59" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>427</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>79</v>
@@ -10042,10 +10040,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="B60" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10071,14 +10069,14 @@
         <v>177</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>79</v>
@@ -10127,7 +10125,7 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -10148,10 +10146,10 @@
         <v>79</v>
       </c>
       <c r="AM60" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AN60" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>79</v>
@@ -10162,10 +10160,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="B61" t="s" s="2">
         <v>436</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>437</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10191,14 +10189,14 @@
         <v>105</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>79</v>
@@ -10247,7 +10245,7 @@
         <v>79</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -10268,10 +10266,10 @@
         <v>79</v>
       </c>
       <c r="AM61" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AN61" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>443</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>79</v>
@@ -10282,10 +10280,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="B62" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10308,19 +10306,19 @@
         <v>92</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="N62" t="s" s="2">
+      <c r="O62" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>79</v>
@@ -10369,7 +10367,7 @@
         <v>79</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -10390,10 +10388,10 @@
         <v>79</v>
       </c>
       <c r="AM62" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AN62" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>79</v>
@@ -10404,10 +10402,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="B63" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>455</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10433,16 +10431,16 @@
         <v>105</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="N63" t="s" s="2">
+      <c r="O63" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>79</v>
@@ -10491,7 +10489,7 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -10512,10 +10510,10 @@
         <v>79</v>
       </c>
       <c r="AM63" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="AN63" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>79</v>
@@ -10526,10 +10524,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10555,16 +10553,16 @@
         <v>138</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="N64" t="s" s="2">
+      <c r="O64" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>79</v>
@@ -10574,46 +10572,46 @@
         <v>79</v>
       </c>
       <c r="S64" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="T64" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF64" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="U64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF64" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -10634,13 +10632,13 @@
         <v>79</v>
       </c>
       <c r="AM64" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="AN64" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="AN64" t="s" s="2">
+      <c r="AO64" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>356</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>79</v>
@@ -10648,10 +10646,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10677,13 +10675,13 @@
         <v>105</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="M65" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="N65" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10697,43 +10695,43 @@
         <v>79</v>
       </c>
       <c r="T65" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF65" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="U65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10754,13 +10752,13 @@
         <v>79</v>
       </c>
       <c r="AM65" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AN65" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="AN65" t="s" s="2">
+      <c r="AO65" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="AO65" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>79</v>
@@ -10768,10 +10766,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10794,13 +10792,13 @@
         <v>92</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10851,7 +10849,7 @@
         <v>79</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10872,13 +10870,13 @@
         <v>79</v>
       </c>
       <c r="AM66" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AN66" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AN66" t="s" s="2">
+      <c r="AO66" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>374</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>79</v>
@@ -10886,10 +10884,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10912,16 +10910,16 @@
         <v>92</v>
       </c>
       <c r="K67" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="L67" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="L67" t="s" s="2">
+      <c r="M67" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="M67" t="s" s="2">
+      <c r="N67" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10971,7 +10969,7 @@
         <v>79</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10992,13 +10990,13 @@
         <v>79</v>
       </c>
       <c r="AM67" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AN67" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="AN67" t="s" s="2">
+      <c r="AO67" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>79</v>
@@ -11006,13 +11004,13 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="C68" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="C68" t="s" s="2">
-        <v>470</v>
       </c>
       <c r="D68" t="s" s="2">
         <v>79</v>
@@ -11034,17 +11032,17 @@
         <v>92</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>79</v>
@@ -11093,7 +11091,7 @@
         <v>79</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -11102,36 +11100,36 @@
         <v>81</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="AM68" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AN68" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="AN68" t="s" s="2">
+      <c r="AO68" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="AO68" t="s" s="2">
+      <c r="AP68" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="AP68" t="s" s="2">
-        <v>312</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11246,10 +11244,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11366,10 +11364,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11395,16 +11393,16 @@
         <v>177</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="N71" t="s" s="2">
+      <c r="O71" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>79</v>
@@ -11429,31 +11427,31 @@
         <v>79</v>
       </c>
       <c r="X71" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="Y71" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="Y71" t="s" s="2">
+      <c r="Z71" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="Z71" t="s" s="2">
+      <c r="AA71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF71" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -11477,7 +11475,7 @@
         <v>200</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>79</v>
@@ -11488,10 +11486,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11514,19 +11512,19 @@
         <v>92</v>
       </c>
       <c r="K72" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="L72" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="L72" t="s" s="2">
+      <c r="M72" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="N72" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="N72" t="s" s="2">
+      <c r="O72" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>79</v>
@@ -11554,28 +11552,28 @@
         <v>159</v>
       </c>
       <c r="Y72" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="Z72" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="Z72" t="s" s="2">
+      <c r="AA72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF72" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>343</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -11596,10 +11594,10 @@
         <v>79</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>79</v>
@@ -11610,10 +11608,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11728,10 +11726,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11848,10 +11846,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11877,16 +11875,16 @@
         <v>155</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="N75" t="s" s="2">
+      <c r="O75" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>79</v>
@@ -11935,7 +11933,7 @@
         <v>79</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11956,10 +11954,10 @@
         <v>79</v>
       </c>
       <c r="AM75" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AN75" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>79</v>
@@ -11970,10 +11968,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12088,10 +12086,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12208,10 +12206,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12237,16 +12235,16 @@
         <v>138</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="N78" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="N78" t="s" s="2">
+      <c r="O78" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>79</v>
@@ -12256,46 +12254,46 @@
         <v>79</v>
       </c>
       <c r="S78" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF78" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="T78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF78" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -12316,10 +12314,10 @@
         <v>79</v>
       </c>
       <c r="AM78" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AN78" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>79</v>
@@ -12330,10 +12328,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12359,13 +12357,13 @@
         <v>105</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="M79" t="s" s="2">
+      <c r="N79" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>424</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -12415,7 +12413,7 @@
         <v>79</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -12436,10 +12434,10 @@
         <v>79</v>
       </c>
       <c r="AM79" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AN79" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="AN79" t="s" s="2">
-        <v>427</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>79</v>
@@ -12450,10 +12448,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12479,14 +12477,14 @@
         <v>177</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>79</v>
@@ -12535,7 +12533,7 @@
         <v>79</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -12556,10 +12554,10 @@
         <v>79</v>
       </c>
       <c r="AM80" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AN80" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="AN80" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>79</v>
@@ -12570,10 +12568,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12599,14 +12597,14 @@
         <v>105</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>79</v>
@@ -12655,7 +12653,7 @@
         <v>79</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12676,10 +12674,10 @@
         <v>79</v>
       </c>
       <c r="AM81" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AN81" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>443</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>79</v>
@@ -12690,10 +12688,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12716,19 +12714,19 @@
         <v>92</v>
       </c>
       <c r="K82" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="L82" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="L82" t="s" s="2">
+      <c r="M82" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="M82" t="s" s="2">
+      <c r="N82" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="N82" t="s" s="2">
+      <c r="O82" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>79</v>
@@ -12777,7 +12775,7 @@
         <v>79</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12798,10 +12796,10 @@
         <v>79</v>
       </c>
       <c r="AM82" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AN82" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>79</v>
@@ -12812,10 +12810,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12841,16 +12839,16 @@
         <v>105</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="M83" t="s" s="2">
+      <c r="N83" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="N83" t="s" s="2">
+      <c r="O83" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>79</v>
@@ -12899,7 +12897,7 @@
         <v>79</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12920,10 +12918,10 @@
         <v>79</v>
       </c>
       <c r="AM83" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="AN83" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>79</v>
@@ -12934,10 +12932,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12963,16 +12961,16 @@
         <v>138</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="N84" t="s" s="2">
+      <c r="O84" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>79</v>
@@ -12982,46 +12980,46 @@
         <v>79</v>
       </c>
       <c r="S84" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="T84" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="U84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF84" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="U84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF84" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -13042,13 +13040,13 @@
         <v>79</v>
       </c>
       <c r="AM84" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="AN84" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="AN84" t="s" s="2">
+      <c r="AO84" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="AO84" t="s" s="2">
-        <v>356</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>79</v>
@@ -13056,10 +13054,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13085,13 +13083,13 @@
         <v>105</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="M85" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="N85" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -13105,43 +13103,43 @@
         <v>79</v>
       </c>
       <c r="T85" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF85" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="U85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF85" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -13162,13 +13160,13 @@
         <v>79</v>
       </c>
       <c r="AM85" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AN85" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="AN85" t="s" s="2">
+      <c r="AO85" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="AO85" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="AP85" t="s" s="2">
         <v>79</v>
@@ -13176,10 +13174,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13202,13 +13200,13 @@
         <v>92</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -13259,7 +13257,7 @@
         <v>79</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -13280,13 +13278,13 @@
         <v>79</v>
       </c>
       <c r="AM86" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AN86" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AN86" t="s" s="2">
+      <c r="AO86" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="AO86" t="s" s="2">
-        <v>374</v>
       </c>
       <c r="AP86" t="s" s="2">
         <v>79</v>
@@ -13294,10 +13292,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13320,16 +13318,16 @@
         <v>92</v>
       </c>
       <c r="K87" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="L87" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="L87" t="s" s="2">
+      <c r="M87" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="M87" t="s" s="2">
+      <c r="N87" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -13379,7 +13377,7 @@
         <v>79</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -13400,13 +13398,13 @@
         <v>79</v>
       </c>
       <c r="AM87" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AN87" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="AN87" t="s" s="2">
+      <c r="AO87" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="AO87" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>79</v>
@@ -13414,13 +13412,13 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="C88" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="B88" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="C88" t="s" s="2">
-        <v>495</v>
       </c>
       <c r="D88" t="s" s="2">
         <v>79</v>
@@ -13442,17 +13440,17 @@
         <v>92</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>79</v>
@@ -13501,7 +13499,7 @@
         <v>79</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -13510,7 +13508,7 @@
         <v>81</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>103</v>
@@ -13522,24 +13520,24 @@
         <v>79</v>
       </c>
       <c r="AM88" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AN88" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="AN88" t="s" s="2">
+      <c r="AO88" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="AO88" t="s" s="2">
+      <c r="AP88" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="AP88" t="s" s="2">
-        <v>312</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13654,10 +13652,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13774,10 +13772,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13803,16 +13801,16 @@
         <v>177</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="N91" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="N91" t="s" s="2">
+      <c r="O91" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>79</v>
@@ -13837,31 +13835,31 @@
         <v>79</v>
       </c>
       <c r="X91" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="Y91" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="Y91" t="s" s="2">
+      <c r="Z91" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="Z91" t="s" s="2">
+      <c r="AA91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF91" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="AA91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF91" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13885,7 +13883,7 @@
         <v>200</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>79</v>
@@ -13896,10 +13894,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13922,19 +13920,19 @@
         <v>92</v>
       </c>
       <c r="K92" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="L92" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="L92" t="s" s="2">
+      <c r="M92" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="M92" t="s" s="2">
+      <c r="N92" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="N92" t="s" s="2">
+      <c r="O92" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>79</v>
@@ -13944,7 +13942,7 @@
         <v>79</v>
       </c>
       <c r="S92" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="T92" t="s" s="2">
         <v>79</v>
@@ -13962,28 +13960,28 @@
         <v>159</v>
       </c>
       <c r="Y92" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="Z92" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="Z92" t="s" s="2">
+      <c r="AA92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF92" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="AA92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF92" t="s" s="2">
-        <v>343</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -14004,10 +14002,10 @@
         <v>79</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>79</v>
@@ -14018,10 +14016,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14047,16 +14045,16 @@
         <v>138</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="M93" t="s" s="2">
+      <c r="N93" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="N93" t="s" s="2">
+      <c r="O93" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="O93" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>79</v>
@@ -14066,46 +14064,46 @@
         <v>79</v>
       </c>
       <c r="S93" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="T93" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="U93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF93" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="U93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF93" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -14126,13 +14124,13 @@
         <v>79</v>
       </c>
       <c r="AM93" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="AN93" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="AN93" t="s" s="2">
+      <c r="AO93" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="AO93" t="s" s="2">
-        <v>356</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>79</v>
@@ -14140,10 +14138,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14169,13 +14167,13 @@
         <v>105</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="M94" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="N94" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -14189,43 +14187,43 @@
         <v>79</v>
       </c>
       <c r="T94" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF94" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="U94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF94" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -14246,13 +14244,13 @@
         <v>79</v>
       </c>
       <c r="AM94" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AN94" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="AN94" t="s" s="2">
+      <c r="AO94" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="AO94" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>79</v>
@@ -14260,10 +14258,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14286,13 +14284,13 @@
         <v>92</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L95" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="M95" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -14343,7 +14341,7 @@
         <v>79</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -14364,13 +14362,13 @@
         <v>79</v>
       </c>
       <c r="AM95" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AN95" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AN95" t="s" s="2">
+      <c r="AO95" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="AO95" t="s" s="2">
-        <v>374</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>79</v>
@@ -14378,10 +14376,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14404,16 +14402,16 @@
         <v>92</v>
       </c>
       <c r="K96" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="L96" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="L96" t="s" s="2">
+      <c r="M96" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="M96" t="s" s="2">
+      <c r="N96" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -14463,7 +14461,7 @@
         <v>79</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -14484,13 +14482,13 @@
         <v>79</v>
       </c>
       <c r="AM96" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AN96" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="AN96" t="s" s="2">
+      <c r="AO96" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="AO96" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>79</v>
@@ -14498,13 +14496,13 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="C97" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="B97" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="C97" t="s" s="2">
-        <v>508</v>
       </c>
       <c r="D97" t="s" s="2">
         <v>79</v>
@@ -14526,17 +14524,17 @@
         <v>92</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>79</v>
@@ -14585,7 +14583,7 @@
         <v>79</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -14594,7 +14592,7 @@
         <v>81</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AJ97" t="s" s="2">
         <v>103</v>
@@ -14606,24 +14604,24 @@
         <v>79</v>
       </c>
       <c r="AM97" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AN97" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="AN97" t="s" s="2">
+      <c r="AO97" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="AO97" t="s" s="2">
+      <c r="AP97" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="AP97" t="s" s="2">
-        <v>312</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14738,10 +14736,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14858,10 +14856,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14887,16 +14885,16 @@
         <v>177</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="M100" t="s" s="2">
+      <c r="N100" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="N100" t="s" s="2">
+      <c r="O100" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>79</v>
@@ -14921,31 +14919,31 @@
         <v>79</v>
       </c>
       <c r="X100" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="Y100" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="Y100" t="s" s="2">
+      <c r="Z100" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="Z100" t="s" s="2">
+      <c r="AA100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF100" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="AA100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF100" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14969,7 +14967,7 @@
         <v>200</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>79</v>
@@ -14980,10 +14978,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15006,19 +15004,19 @@
         <v>92</v>
       </c>
       <c r="K101" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="L101" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="L101" t="s" s="2">
+      <c r="M101" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="M101" t="s" s="2">
+      <c r="N101" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="N101" t="s" s="2">
+      <c r="O101" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>79</v>
@@ -15028,7 +15026,7 @@
         <v>79</v>
       </c>
       <c r="S101" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="T101" t="s" s="2">
         <v>79</v>
@@ -15046,28 +15044,28 @@
         <v>159</v>
       </c>
       <c r="Y101" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="Z101" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="Z101" t="s" s="2">
+      <c r="AA101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF101" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="AA101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF101" t="s" s="2">
-        <v>343</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -15088,10 +15086,10 @@
         <v>79</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>79</v>
@@ -15102,10 +15100,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15131,16 +15129,16 @@
         <v>138</v>
       </c>
       <c r="L102" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="M102" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="M102" t="s" s="2">
+      <c r="N102" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="N102" t="s" s="2">
+      <c r="O102" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="O102" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>79</v>
@@ -15150,46 +15148,46 @@
         <v>79</v>
       </c>
       <c r="S102" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="T102" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="U102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF102" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="U102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF102" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -15210,13 +15208,13 @@
         <v>79</v>
       </c>
       <c r="AM102" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="AN102" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="AN102" t="s" s="2">
+      <c r="AO102" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="AO102" t="s" s="2">
-        <v>356</v>
       </c>
       <c r="AP102" t="s" s="2">
         <v>79</v>
@@ -15224,10 +15222,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15253,13 +15251,13 @@
         <v>105</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="M103" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="N103" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -15273,43 +15271,43 @@
         <v>79</v>
       </c>
       <c r="T103" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="U103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF103" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="U103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF103" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -15330,13 +15328,13 @@
         <v>79</v>
       </c>
       <c r="AM103" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AN103" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="AN103" t="s" s="2">
+      <c r="AO103" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="AO103" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="AP103" t="s" s="2">
         <v>79</v>
@@ -15344,10 +15342,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15370,13 +15368,13 @@
         <v>92</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="M104" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="M104" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -15427,7 +15425,7 @@
         <v>79</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -15448,13 +15446,13 @@
         <v>79</v>
       </c>
       <c r="AM104" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AN104" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AN104" t="s" s="2">
+      <c r="AO104" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="AO104" t="s" s="2">
-        <v>374</v>
       </c>
       <c r="AP104" t="s" s="2">
         <v>79</v>
@@ -15462,10 +15460,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15488,16 +15486,16 @@
         <v>92</v>
       </c>
       <c r="K105" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="L105" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="L105" t="s" s="2">
+      <c r="M105" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="M105" t="s" s="2">
+      <c r="N105" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -15547,7 +15545,7 @@
         <v>79</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -15568,13 +15566,13 @@
         <v>79</v>
       </c>
       <c r="AM105" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AN105" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="AN105" t="s" s="2">
+      <c r="AO105" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="AO105" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="AP105" t="s" s="2">
         <v>79</v>
@@ -15582,10 +15580,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15608,26 +15606,26 @@
         <v>92</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="L106" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="M106" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="M106" t="s" s="2">
+      <c r="N106" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="N106" t="s" s="2">
+      <c r="O106" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="O106" t="s" s="2">
+      <c r="P106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q106" t="s" s="2">
         <v>523</v>
       </c>
-      <c r="P106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q106" t="s" s="2">
-        <v>524</v>
-      </c>
       <c r="R106" t="s" s="2">
         <v>79</v>
       </c>
@@ -15671,7 +15669,7 @@
         <v>79</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15689,27 +15687,27 @@
         <v>79</v>
       </c>
       <c r="AL106" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="AM106" t="s" s="2">
         <v>525</v>
       </c>
-      <c r="AM106" t="s" s="2">
+      <c r="AN106" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="AN106" t="s" s="2">
+      <c r="AO106" t="s" s="2">
         <v>527</v>
       </c>
-      <c r="AO106" t="s" s="2">
+      <c r="AP106" t="s" s="2">
         <v>528</v>
-      </c>
-      <c r="AP106" t="s" s="2">
-        <v>529</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15732,19 +15730,19 @@
         <v>92</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="L107" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="M107" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="M107" t="s" s="2">
+      <c r="N107" t="s" s="2">
         <v>532</v>
       </c>
-      <c r="N107" t="s" s="2">
+      <c r="O107" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>534</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>79</v>
@@ -15772,16 +15770,16 @@
         <v>167</v>
       </c>
       <c r="Y107" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="Z107" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="Z107" t="s" s="2">
+      <c r="AA107" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB107" t="s" s="2">
         <v>536</v>
-      </c>
-      <c r="AA107" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB107" t="s" s="2">
-        <v>537</v>
       </c>
       <c r="AC107" s="2"/>
       <c r="AD107" t="s" s="2">
@@ -15791,7 +15789,7 @@
         <v>118</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15812,27 +15810,27 @@
         <v>79</v>
       </c>
       <c r="AM107" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="AN107" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="AN107" t="s" s="2">
-        <v>539</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AP107" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="C108" t="s" s="2">
         <v>541</v>
-      </c>
-      <c r="B108" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="C108" t="s" s="2">
-        <v>542</v>
       </c>
       <c r="D108" t="s" s="2">
         <v>79</v>
@@ -15854,19 +15852,19 @@
         <v>92</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="M108" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="N108" t="s" s="2">
         <v>532</v>
       </c>
-      <c r="N108" t="s" s="2">
+      <c r="O108" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="O108" t="s" s="2">
-        <v>534</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>79</v>
@@ -15891,11 +15889,11 @@
         <v>79</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="Y108" s="2"/>
       <c r="Z108" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>79</v>
@@ -15913,7 +15911,7 @@
         <v>79</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15934,24 +15932,24 @@
         <v>79</v>
       </c>
       <c r="AM108" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="AN108" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="AN108" t="s" s="2">
-        <v>539</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AP108" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="B109" t="s" s="2">
         <v>545</v>
-      </c>
-      <c r="B109" t="s" s="2">
-        <v>546</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -16066,10 +16064,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="B110" t="s" s="2">
         <v>547</v>
-      </c>
-      <c r="B110" t="s" s="2">
-        <v>548</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -16184,13 +16182,13 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="B111" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="C111" t="s" s="2">
         <v>549</v>
-      </c>
-      <c r="B111" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="C111" t="s" s="2">
-        <v>550</v>
       </c>
       <c r="D111" t="s" s="2">
         <v>79</v>
@@ -16212,13 +16210,13 @@
         <v>79</v>
       </c>
       <c r="K111" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="L111" t="s" s="2">
         <v>551</v>
       </c>
-      <c r="L111" t="s" s="2">
+      <c r="M111" t="s" s="2">
         <v>552</v>
-      </c>
-      <c r="M111" t="s" s="2">
-        <v>553</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -16304,10 +16302,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="B112" t="s" s="2">
         <v>554</v>
-      </c>
-      <c r="B112" t="s" s="2">
-        <v>555</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16422,10 +16420,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="B113" t="s" s="2">
         <v>556</v>
-      </c>
-      <c r="B113" t="s" s="2">
-        <v>557</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16514,7 +16512,7 @@
         <v>81</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>209</v>
+        <v>79</v>
       </c>
       <c r="AJ113" t="s" s="2">
         <v>120</v>
@@ -16540,10 +16538,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="B114" t="s" s="2">
         <v>558</v>
-      </c>
-      <c r="B114" t="s" s="2">
-        <v>559</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16569,13 +16567,13 @@
         <v>138</v>
       </c>
       <c r="L114" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="M114" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="M114" t="s" s="2">
+      <c r="N114" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -16583,7 +16581,7 @@
       </c>
       <c r="Q114" s="2"/>
       <c r="R114" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="S114" t="s" s="2">
         <v>79</v>
@@ -16625,7 +16623,7 @@
         <v>79</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>91</v>
@@ -16660,10 +16658,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="B115" t="s" s="2">
         <v>561</v>
-      </c>
-      <c r="B115" t="s" s="2">
-        <v>562</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16689,10 +16687,10 @@
         <v>177</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>234</v>
+        <v>562</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -16704,7 +16702,7 @@
         <v>79</v>
       </c>
       <c r="S115" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="T115" t="s" s="2">
         <v>79</v>
@@ -16719,7 +16717,7 @@
         <v>79</v>
       </c>
       <c r="X115" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="Y115" s="2"/>
       <c r="Z115" t="s" s="2">
@@ -16741,7 +16739,7 @@
         <v>79</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -16750,7 +16748,7 @@
         <v>91</v>
       </c>
       <c r="AI115" t="s" s="2">
-        <v>209</v>
+        <v>79</v>
       </c>
       <c r="AJ115" t="s" s="2">
         <v>103</v>
@@ -16805,16 +16803,16 @@
         <v>155</v>
       </c>
       <c r="L116" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="M116" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="M116" t="s" s="2">
+      <c r="N116" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="N116" t="s" s="2">
+      <c r="O116" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="O116" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>79</v>
@@ -16863,7 +16861,7 @@
         <v>79</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -16884,10 +16882,10 @@
         <v>79</v>
       </c>
       <c r="AM116" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AN116" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="AN116" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>79</v>
@@ -17165,16 +17163,16 @@
         <v>138</v>
       </c>
       <c r="L119" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="M119" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="M119" t="s" s="2">
+      <c r="N119" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="N119" t="s" s="2">
+      <c r="O119" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="O119" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>79</v>
@@ -17223,7 +17221,7 @@
         <v>79</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -17244,10 +17242,10 @@
         <v>79</v>
       </c>
       <c r="AM119" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AN119" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="AN119" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>79</v>
@@ -17287,13 +17285,13 @@
         <v>105</v>
       </c>
       <c r="L120" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="M120" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="M120" t="s" s="2">
+      <c r="N120" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="N120" t="s" s="2">
-        <v>424</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
@@ -17343,7 +17341,7 @@
         <v>79</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -17364,10 +17362,10 @@
         <v>79</v>
       </c>
       <c r="AM120" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AN120" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="AN120" t="s" s="2">
-        <v>427</v>
       </c>
       <c r="AO120" t="s" s="2">
         <v>79</v>
@@ -17410,11 +17408,11 @@
         <v>576</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>79</v>
@@ -17463,7 +17461,7 @@
         <v>79</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -17484,10 +17482,10 @@
         <v>79</v>
       </c>
       <c r="AM121" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AN121" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="AN121" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>79</v>
@@ -17527,14 +17525,14 @@
         <v>105</v>
       </c>
       <c r="L122" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="M122" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="M122" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>79</v>
@@ -17583,7 +17581,7 @@
         <v>79</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -17604,10 +17602,10 @@
         <v>79</v>
       </c>
       <c r="AM122" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AN122" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="AN122" t="s" s="2">
-        <v>443</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>79</v>
@@ -17644,19 +17642,19 @@
         <v>92</v>
       </c>
       <c r="K123" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="L123" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="L123" t="s" s="2">
+      <c r="M123" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="M123" t="s" s="2">
+      <c r="N123" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="N123" t="s" s="2">
+      <c r="O123" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="O123" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>79</v>
@@ -17705,7 +17703,7 @@
         <v>79</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -17726,10 +17724,10 @@
         <v>79</v>
       </c>
       <c r="AM123" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AN123" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="AN123" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>79</v>
@@ -17769,16 +17767,16 @@
         <v>105</v>
       </c>
       <c r="L124" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="M124" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="M124" t="s" s="2">
+      <c r="N124" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="N124" t="s" s="2">
+      <c r="O124" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="O124" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>79</v>
@@ -17827,7 +17825,7 @@
         <v>79</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
@@ -17848,10 +17846,10 @@
         <v>79</v>
       </c>
       <c r="AM124" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="AN124" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="AN124" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="AO124" t="s" s="2">
         <v>79</v>
@@ -17865,7 +17863,7 @@
         <v>583</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C125" t="s" s="2">
         <v>584</v>
@@ -17890,19 +17888,19 @@
         <v>92</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="L125" t="s" s="2">
         <v>585</v>
       </c>
       <c r="M125" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="N125" t="s" s="2">
         <v>532</v>
       </c>
-      <c r="N125" t="s" s="2">
+      <c r="O125" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="O125" t="s" s="2">
-        <v>534</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>79</v>
@@ -17927,7 +17925,7 @@
         <v>79</v>
       </c>
       <c r="X125" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="Y125" s="2"/>
       <c r="Z125" t="s" s="2">
@@ -17949,7 +17947,7 @@
         <v>79</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -17970,16 +17968,16 @@
         <v>79</v>
       </c>
       <c r="AM125" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="AN125" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="AN125" t="s" s="2">
-        <v>539</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AP125" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="126" hidden="true">
@@ -17987,7 +17985,7 @@
         <v>587</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -18105,7 +18103,7 @@
         <v>588</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -18251,16 +18249,16 @@
         <v>155</v>
       </c>
       <c r="L128" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="M128" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="M128" t="s" s="2">
+      <c r="N128" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="N128" t="s" s="2">
+      <c r="O128" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="O128" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>79</v>
@@ -18309,7 +18307,7 @@
         <v>79</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -18330,10 +18328,10 @@
         <v>79</v>
       </c>
       <c r="AM128" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AN128" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="AN128" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="AO128" t="s" s="2">
         <v>79</v>
@@ -18611,16 +18609,16 @@
         <v>138</v>
       </c>
       <c r="L131" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="M131" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="M131" t="s" s="2">
+      <c r="N131" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="N131" t="s" s="2">
+      <c r="O131" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="O131" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>79</v>
@@ -18669,7 +18667,7 @@
         <v>79</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -18690,10 +18688,10 @@
         <v>79</v>
       </c>
       <c r="AM131" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AN131" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="AN131" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="AO131" t="s" s="2">
         <v>79</v>
@@ -18733,13 +18731,13 @@
         <v>105</v>
       </c>
       <c r="L132" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="M132" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="M132" t="s" s="2">
+      <c r="N132" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="N132" t="s" s="2">
-        <v>424</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -18789,7 +18787,7 @@
         <v>79</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -18810,10 +18808,10 @@
         <v>79</v>
       </c>
       <c r="AM132" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AN132" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="AN132" t="s" s="2">
-        <v>427</v>
       </c>
       <c r="AO132" t="s" s="2">
         <v>79</v>
@@ -18856,11 +18854,11 @@
         <v>576</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>79</v>
@@ -18909,7 +18907,7 @@
         <v>79</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -18930,10 +18928,10 @@
         <v>79</v>
       </c>
       <c r="AM133" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AN133" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="AN133" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="AO133" t="s" s="2">
         <v>79</v>
@@ -18973,14 +18971,14 @@
         <v>105</v>
       </c>
       <c r="L134" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="M134" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="M134" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>79</v>
@@ -19029,7 +19027,7 @@
         <v>79</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -19050,10 +19048,10 @@
         <v>79</v>
       </c>
       <c r="AM134" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AN134" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="AN134" t="s" s="2">
-        <v>443</v>
       </c>
       <c r="AO134" t="s" s="2">
         <v>79</v>
@@ -19090,19 +19088,19 @@
         <v>92</v>
       </c>
       <c r="K135" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="L135" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="L135" t="s" s="2">
+      <c r="M135" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="M135" t="s" s="2">
+      <c r="N135" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="N135" t="s" s="2">
+      <c r="O135" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="O135" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>79</v>
@@ -19151,7 +19149,7 @@
         <v>79</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -19172,10 +19170,10 @@
         <v>79</v>
       </c>
       <c r="AM135" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AN135" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="AN135" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>79</v>
@@ -19215,16 +19213,16 @@
         <v>105</v>
       </c>
       <c r="L136" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="M136" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="M136" t="s" s="2">
+      <c r="N136" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="N136" t="s" s="2">
+      <c r="O136" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="O136" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>79</v>
@@ -19273,7 +19271,7 @@
         <v>79</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -19294,10 +19292,10 @@
         <v>79</v>
       </c>
       <c r="AM136" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="AN136" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="AN136" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="AO136" t="s" s="2">
         <v>79</v>
@@ -19311,7 +19309,7 @@
         <v>598</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C137" t="s" s="2">
         <v>599</v>
@@ -19336,19 +19334,19 @@
         <v>92</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="L137" t="s" s="2">
         <v>600</v>
       </c>
       <c r="M137" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="N137" t="s" s="2">
         <v>532</v>
       </c>
-      <c r="N137" t="s" s="2">
+      <c r="O137" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="O137" t="s" s="2">
-        <v>534</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>79</v>
@@ -19373,7 +19371,7 @@
         <v>79</v>
       </c>
       <c r="X137" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="Y137" s="2"/>
       <c r="Z137" t="s" s="2">
@@ -19395,7 +19393,7 @@
         <v>79</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -19416,16 +19414,16 @@
         <v>79</v>
       </c>
       <c r="AM137" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="AN137" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="AN137" t="s" s="2">
-        <v>539</v>
       </c>
       <c r="AO137" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AP137" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="138" hidden="true">
@@ -19433,7 +19431,7 @@
         <v>602</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19551,7 +19549,7 @@
         <v>603</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19697,16 +19695,16 @@
         <v>155</v>
       </c>
       <c r="L140" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="M140" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="M140" t="s" s="2">
+      <c r="N140" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="N140" t="s" s="2">
+      <c r="O140" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="O140" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>79</v>
@@ -19755,7 +19753,7 @@
         <v>79</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -19776,10 +19774,10 @@
         <v>79</v>
       </c>
       <c r="AM140" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AN140" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="AN140" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="AO140" t="s" s="2">
         <v>79</v>
@@ -20057,16 +20055,16 @@
         <v>138</v>
       </c>
       <c r="L143" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="M143" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="M143" t="s" s="2">
+      <c r="N143" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="N143" t="s" s="2">
+      <c r="O143" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="O143" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>79</v>
@@ -20115,7 +20113,7 @@
         <v>79</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
@@ -20136,10 +20134,10 @@
         <v>79</v>
       </c>
       <c r="AM143" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AN143" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="AN143" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="AO143" t="s" s="2">
         <v>79</v>
@@ -20179,13 +20177,13 @@
         <v>105</v>
       </c>
       <c r="L144" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="M144" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="M144" t="s" s="2">
+      <c r="N144" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="N144" t="s" s="2">
-        <v>424</v>
       </c>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
@@ -20235,7 +20233,7 @@
         <v>79</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>80</v>
@@ -20256,10 +20254,10 @@
         <v>79</v>
       </c>
       <c r="AM144" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AN144" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="AN144" t="s" s="2">
-        <v>427</v>
       </c>
       <c r="AO144" t="s" s="2">
         <v>79</v>
@@ -20302,11 +20300,11 @@
         <v>576</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>79</v>
@@ -20355,7 +20353,7 @@
         <v>79</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>80</v>
@@ -20376,10 +20374,10 @@
         <v>79</v>
       </c>
       <c r="AM145" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AN145" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="AN145" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="AO145" t="s" s="2">
         <v>79</v>
@@ -20419,14 +20417,14 @@
         <v>105</v>
       </c>
       <c r="L146" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="M146" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="M146" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>79</v>
@@ -20475,7 +20473,7 @@
         <v>79</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -20496,10 +20494,10 @@
         <v>79</v>
       </c>
       <c r="AM146" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AN146" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="AN146" t="s" s="2">
-        <v>443</v>
       </c>
       <c r="AO146" t="s" s="2">
         <v>79</v>
@@ -20536,19 +20534,19 @@
         <v>92</v>
       </c>
       <c r="K147" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="L147" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="L147" t="s" s="2">
+      <c r="M147" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="M147" t="s" s="2">
+      <c r="N147" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="N147" t="s" s="2">
+      <c r="O147" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="O147" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>79</v>
@@ -20597,7 +20595,7 @@
         <v>79</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
@@ -20618,10 +20616,10 @@
         <v>79</v>
       </c>
       <c r="AM147" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AN147" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="AN147" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="AO147" t="s" s="2">
         <v>79</v>
@@ -20661,16 +20659,16 @@
         <v>105</v>
       </c>
       <c r="L148" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="M148" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="M148" t="s" s="2">
+      <c r="N148" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="N148" t="s" s="2">
+      <c r="O148" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="O148" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>79</v>
@@ -20719,7 +20717,7 @@
         <v>79</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
@@ -20740,10 +20738,10 @@
         <v>79</v>
       </c>
       <c r="AM148" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="AN148" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="AN148" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="AO148" t="s" s="2">
         <v>79</v>
@@ -20757,7 +20755,7 @@
         <v>613</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C149" t="s" s="2">
         <v>614</v>
@@ -20782,19 +20780,19 @@
         <v>92</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="L149" t="s" s="2">
         <v>615</v>
       </c>
       <c r="M149" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="N149" t="s" s="2">
         <v>532</v>
       </c>
-      <c r="N149" t="s" s="2">
+      <c r="O149" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="O149" t="s" s="2">
-        <v>534</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>79</v>
@@ -20819,7 +20817,7 @@
         <v>79</v>
       </c>
       <c r="X149" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="Y149" s="2"/>
       <c r="Z149" t="s" s="2">
@@ -20841,7 +20839,7 @@
         <v>79</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -20862,16 +20860,16 @@
         <v>618</v>
       </c>
       <c r="AM149" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="AN149" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="AN149" t="s" s="2">
-        <v>539</v>
       </c>
       <c r="AO149" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AP149" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="150" hidden="true">
@@ -20879,7 +20877,7 @@
         <v>619</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20997,7 +20995,7 @@
         <v>620</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -21086,7 +21084,7 @@
         <v>81</v>
       </c>
       <c r="AI151" t="s" s="2">
-        <v>209</v>
+        <v>79</v>
       </c>
       <c r="AJ151" t="s" s="2">
         <v>120</v>
@@ -21115,10 +21113,10 @@
         <v>621</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D152" t="s" s="2">
         <v>79</v>
@@ -21140,13 +21138,13 @@
         <v>79</v>
       </c>
       <c r="K152" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="L152" t="s" s="2">
         <v>551</v>
       </c>
-      <c r="L152" t="s" s="2">
+      <c r="M152" t="s" s="2">
         <v>552</v>
-      </c>
-      <c r="M152" t="s" s="2">
-        <v>553</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -21206,7 +21204,7 @@
         <v>81</v>
       </c>
       <c r="AI152" t="s" s="2">
-        <v>209</v>
+        <v>79</v>
       </c>
       <c r="AJ152" t="s" s="2">
         <v>120</v>
@@ -21235,7 +21233,7 @@
         <v>622</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21353,7 +21351,7 @@
         <v>623</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21442,7 +21440,7 @@
         <v>81</v>
       </c>
       <c r="AI154" t="s" s="2">
-        <v>209</v>
+        <v>79</v>
       </c>
       <c r="AJ154" t="s" s="2">
         <v>120</v>
@@ -21471,7 +21469,7 @@
         <v>624</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21497,13 +21495,13 @@
         <v>138</v>
       </c>
       <c r="L155" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="M155" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="M155" t="s" s="2">
+      <c r="N155" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="N155" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
@@ -21511,7 +21509,7 @@
       </c>
       <c r="Q155" s="2"/>
       <c r="R155" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="S155" t="s" s="2">
         <v>79</v>
@@ -21553,7 +21551,7 @@
         <v>79</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>91</v>
@@ -21591,7 +21589,7 @@
         <v>625</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21617,10 +21615,10 @@
         <v>177</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>234</v>
+        <v>562</v>
       </c>
       <c r="N156" s="2"/>
       <c r="O156" s="2"/>
@@ -21647,7 +21645,7 @@
         <v>79</v>
       </c>
       <c r="X156" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="Y156" s="2"/>
       <c r="Z156" t="s" s="2">
@@ -21669,7 +21667,7 @@
         <v>79</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>80</v>
@@ -21678,7 +21676,7 @@
         <v>91</v>
       </c>
       <c r="AI156" t="s" s="2">
-        <v>209</v>
+        <v>79</v>
       </c>
       <c r="AJ156" t="s" s="2">
         <v>103</v>
@@ -21733,16 +21731,16 @@
         <v>155</v>
       </c>
       <c r="L157" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="M157" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="M157" t="s" s="2">
+      <c r="N157" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="N157" t="s" s="2">
+      <c r="O157" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="O157" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>79</v>
@@ -21791,7 +21789,7 @@
         <v>79</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>80</v>
@@ -21800,7 +21798,7 @@
         <v>81</v>
       </c>
       <c r="AI157" t="s" s="2">
-        <v>209</v>
+        <v>79</v>
       </c>
       <c r="AJ157" t="s" s="2">
         <v>103</v>
@@ -21812,10 +21810,10 @@
         <v>79</v>
       </c>
       <c r="AM157" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AN157" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="AN157" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="AO157" t="s" s="2">
         <v>79</v>
@@ -21855,16 +21853,16 @@
         <v>105</v>
       </c>
       <c r="L158" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="M158" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="M158" t="s" s="2">
+      <c r="N158" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="N158" t="s" s="2">
+      <c r="O158" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="O158" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>79</v>
@@ -21913,7 +21911,7 @@
         <v>79</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>80</v>
@@ -21922,7 +21920,7 @@
         <v>91</v>
       </c>
       <c r="AI158" t="s" s="2">
-        <v>209</v>
+        <v>79</v>
       </c>
       <c r="AJ158" t="s" s="2">
         <v>103</v>
@@ -21934,10 +21932,10 @@
         <v>79</v>
       </c>
       <c r="AM158" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="AN158" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="AN158" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="AO158" t="s" s="2">
         <v>79</v>
@@ -21951,7 +21949,7 @@
         <v>628</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C159" t="s" s="2">
         <v>629</v>
@@ -21976,19 +21974,19 @@
         <v>92</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="L159" t="s" s="2">
         <v>630</v>
       </c>
       <c r="M159" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="N159" t="s" s="2">
         <v>532</v>
       </c>
-      <c r="N159" t="s" s="2">
+      <c r="O159" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="O159" t="s" s="2">
-        <v>534</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>79</v>
@@ -22013,7 +22011,7 @@
         <v>79</v>
       </c>
       <c r="X159" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="Y159" s="2"/>
       <c r="Z159" t="s" s="2">
@@ -22035,7 +22033,7 @@
         <v>79</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>80</v>
@@ -22056,16 +22054,16 @@
         <v>79</v>
       </c>
       <c r="AM159" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="AN159" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="AN159" t="s" s="2">
-        <v>539</v>
       </c>
       <c r="AO159" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AP159" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="160" hidden="true">
@@ -22073,7 +22071,7 @@
         <v>633</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -22191,7 +22189,7 @@
         <v>634</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -22280,7 +22278,7 @@
         <v>81</v>
       </c>
       <c r="AI161" t="s" s="2">
-        <v>209</v>
+        <v>79</v>
       </c>
       <c r="AJ161" t="s" s="2">
         <v>120</v>
@@ -22309,10 +22307,10 @@
         <v>635</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C162" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D162" t="s" s="2">
         <v>79</v>
@@ -22334,13 +22332,13 @@
         <v>79</v>
       </c>
       <c r="K162" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="L162" t="s" s="2">
         <v>551</v>
       </c>
-      <c r="L162" t="s" s="2">
+      <c r="M162" t="s" s="2">
         <v>552</v>
-      </c>
-      <c r="M162" t="s" s="2">
-        <v>553</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
@@ -22400,7 +22398,7 @@
         <v>81</v>
       </c>
       <c r="AI162" t="s" s="2">
-        <v>209</v>
+        <v>79</v>
       </c>
       <c r="AJ162" t="s" s="2">
         <v>120</v>
@@ -22429,7 +22427,7 @@
         <v>636</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22547,7 +22545,7 @@
         <v>637</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22636,7 +22634,7 @@
         <v>81</v>
       </c>
       <c r="AI164" t="s" s="2">
-        <v>209</v>
+        <v>79</v>
       </c>
       <c r="AJ164" t="s" s="2">
         <v>120</v>
@@ -22665,7 +22663,7 @@
         <v>638</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22691,13 +22689,13 @@
         <v>138</v>
       </c>
       <c r="L165" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="M165" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="M165" t="s" s="2">
+      <c r="N165" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="N165" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
@@ -22705,7 +22703,7 @@
       </c>
       <c r="Q165" s="2"/>
       <c r="R165" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="S165" t="s" s="2">
         <v>79</v>
@@ -22747,7 +22745,7 @@
         <v>79</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>91</v>
@@ -22785,7 +22783,7 @@
         <v>639</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22811,10 +22809,10 @@
         <v>177</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>234</v>
+        <v>562</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" s="2"/>
@@ -22841,7 +22839,7 @@
         <v>79</v>
       </c>
       <c r="X166" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="Y166" s="2"/>
       <c r="Z166" t="s" s="2">
@@ -22863,7 +22861,7 @@
         <v>79</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>80</v>
@@ -22872,7 +22870,7 @@
         <v>91</v>
       </c>
       <c r="AI166" t="s" s="2">
-        <v>209</v>
+        <v>79</v>
       </c>
       <c r="AJ166" t="s" s="2">
         <v>103</v>
@@ -22927,16 +22925,16 @@
         <v>155</v>
       </c>
       <c r="L167" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="M167" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="M167" t="s" s="2">
+      <c r="N167" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="N167" t="s" s="2">
+      <c r="O167" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="O167" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>79</v>
@@ -22985,7 +22983,7 @@
         <v>79</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>80</v>
@@ -22994,7 +22992,7 @@
         <v>81</v>
       </c>
       <c r="AI167" t="s" s="2">
-        <v>209</v>
+        <v>79</v>
       </c>
       <c r="AJ167" t="s" s="2">
         <v>103</v>
@@ -23006,10 +23004,10 @@
         <v>79</v>
       </c>
       <c r="AM167" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AN167" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="AN167" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="AO167" t="s" s="2">
         <v>79</v>
@@ -23049,16 +23047,16 @@
         <v>105</v>
       </c>
       <c r="L168" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="M168" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="M168" t="s" s="2">
+      <c r="N168" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="N168" t="s" s="2">
+      <c r="O168" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="O168" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>79</v>
@@ -23107,7 +23105,7 @@
         <v>79</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>80</v>
@@ -23116,7 +23114,7 @@
         <v>91</v>
       </c>
       <c r="AI168" t="s" s="2">
-        <v>209</v>
+        <v>79</v>
       </c>
       <c r="AJ168" t="s" s="2">
         <v>103</v>
@@ -23128,10 +23126,10 @@
         <v>79</v>
       </c>
       <c r="AM168" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="AN168" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="AN168" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="AO168" t="s" s="2">
         <v>79</v>
@@ -23145,7 +23143,7 @@
         <v>642</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C169" t="s" s="2">
         <v>643</v>
@@ -23170,19 +23168,19 @@
         <v>92</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="L169" t="s" s="2">
         <v>644</v>
       </c>
       <c r="M169" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="N169" t="s" s="2">
         <v>532</v>
       </c>
-      <c r="N169" t="s" s="2">
+      <c r="O169" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="O169" t="s" s="2">
-        <v>534</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>79</v>
@@ -23207,7 +23205,7 @@
         <v>79</v>
       </c>
       <c r="X169" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="Y169" s="2"/>
       <c r="Z169" t="s" s="2">
@@ -23229,7 +23227,7 @@
         <v>79</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>80</v>
@@ -23250,16 +23248,16 @@
         <v>618</v>
       </c>
       <c r="AM169" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="AN169" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="AN169" t="s" s="2">
-        <v>539</v>
       </c>
       <c r="AO169" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AP169" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="170" hidden="true">
@@ -23267,7 +23265,7 @@
         <v>646</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -23385,7 +23383,7 @@
         <v>647</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23474,7 +23472,7 @@
         <v>81</v>
       </c>
       <c r="AI171" t="s" s="2">
-        <v>209</v>
+        <v>79</v>
       </c>
       <c r="AJ171" t="s" s="2">
         <v>120</v>
@@ -23503,10 +23501,10 @@
         <v>648</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C172" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D172" t="s" s="2">
         <v>79</v>
@@ -23528,13 +23526,13 @@
         <v>79</v>
       </c>
       <c r="K172" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="L172" t="s" s="2">
         <v>551</v>
       </c>
-      <c r="L172" t="s" s="2">
+      <c r="M172" t="s" s="2">
         <v>552</v>
-      </c>
-      <c r="M172" t="s" s="2">
-        <v>553</v>
       </c>
       <c r="N172" s="2"/>
       <c r="O172" s="2"/>
@@ -23594,7 +23592,7 @@
         <v>81</v>
       </c>
       <c r="AI172" t="s" s="2">
-        <v>209</v>
+        <v>79</v>
       </c>
       <c r="AJ172" t="s" s="2">
         <v>120</v>
@@ -23623,7 +23621,7 @@
         <v>649</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23741,7 +23739,7 @@
         <v>650</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23830,7 +23828,7 @@
         <v>81</v>
       </c>
       <c r="AI174" t="s" s="2">
-        <v>209</v>
+        <v>79</v>
       </c>
       <c r="AJ174" t="s" s="2">
         <v>120</v>
@@ -23859,7 +23857,7 @@
         <v>651</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23885,13 +23883,13 @@
         <v>138</v>
       </c>
       <c r="L175" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="M175" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="M175" t="s" s="2">
+      <c r="N175" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="N175" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="O175" s="2"/>
       <c r="P175" t="s" s="2">
@@ -23899,7 +23897,7 @@
       </c>
       <c r="Q175" s="2"/>
       <c r="R175" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="S175" t="s" s="2">
         <v>79</v>
@@ -23941,7 +23939,7 @@
         <v>79</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>91</v>
@@ -23979,7 +23977,7 @@
         <v>652</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -24005,10 +24003,10 @@
         <v>177</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>234</v>
+        <v>562</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
@@ -24035,7 +24033,7 @@
         <v>79</v>
       </c>
       <c r="X176" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="Y176" s="2"/>
       <c r="Z176" t="s" s="2">
@@ -24057,7 +24055,7 @@
         <v>79</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>80</v>
@@ -24066,7 +24064,7 @@
         <v>91</v>
       </c>
       <c r="AI176" t="s" s="2">
-        <v>209</v>
+        <v>79</v>
       </c>
       <c r="AJ176" t="s" s="2">
         <v>103</v>
@@ -24121,16 +24119,16 @@
         <v>155</v>
       </c>
       <c r="L177" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="M177" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="M177" t="s" s="2">
+      <c r="N177" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="N177" t="s" s="2">
+      <c r="O177" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="O177" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="P177" t="s" s="2">
         <v>79</v>
@@ -24179,7 +24177,7 @@
         <v>79</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>80</v>
@@ -24188,7 +24186,7 @@
         <v>81</v>
       </c>
       <c r="AI177" t="s" s="2">
-        <v>209</v>
+        <v>79</v>
       </c>
       <c r="AJ177" t="s" s="2">
         <v>103</v>
@@ -24200,10 +24198,10 @@
         <v>79</v>
       </c>
       <c r="AM177" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AN177" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="AN177" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="AO177" t="s" s="2">
         <v>79</v>
@@ -24243,16 +24241,16 @@
         <v>105</v>
       </c>
       <c r="L178" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="M178" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="M178" t="s" s="2">
+      <c r="N178" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="N178" t="s" s="2">
+      <c r="O178" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="O178" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="P178" t="s" s="2">
         <v>79</v>
@@ -24301,7 +24299,7 @@
         <v>79</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>80</v>
@@ -24310,7 +24308,7 @@
         <v>91</v>
       </c>
       <c r="AI178" t="s" s="2">
-        <v>209</v>
+        <v>79</v>
       </c>
       <c r="AJ178" t="s" s="2">
         <v>103</v>
@@ -24322,10 +24320,10 @@
         <v>79</v>
       </c>
       <c r="AM178" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="AN178" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="AN178" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="AO178" t="s" s="2">
         <v>79</v>
@@ -24339,7 +24337,7 @@
         <v>655</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C179" t="s" s="2">
         <v>656</v>
@@ -24364,19 +24362,19 @@
         <v>92</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="L179" t="s" s="2">
         <v>657</v>
       </c>
       <c r="M179" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="N179" t="s" s="2">
         <v>532</v>
       </c>
-      <c r="N179" t="s" s="2">
+      <c r="O179" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="O179" t="s" s="2">
-        <v>534</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>79</v>
@@ -24404,11 +24402,11 @@
         <v>167</v>
       </c>
       <c r="Y179" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="Z179" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="Z179" t="s" s="2">
-        <v>536</v>
-      </c>
       <c r="AA179" t="s" s="2">
         <v>79</v>
       </c>
@@ -24425,7 +24423,7 @@
         <v>79</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>80</v>
@@ -24446,16 +24444,16 @@
         <v>79</v>
       </c>
       <c r="AM179" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="AN179" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="AN179" t="s" s="2">
-        <v>539</v>
       </c>
       <c r="AO179" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AP179" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="180" hidden="true">
@@ -24463,7 +24461,7 @@
         <v>658</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24581,7 +24579,7 @@
         <v>659</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24670,7 +24668,7 @@
         <v>81</v>
       </c>
       <c r="AI181" t="s" s="2">
-        <v>209</v>
+        <v>79</v>
       </c>
       <c r="AJ181" t="s" s="2">
         <v>120</v>
@@ -24699,10 +24697,10 @@
         <v>660</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C182" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D182" t="s" s="2">
         <v>79</v>
@@ -24724,13 +24722,13 @@
         <v>79</v>
       </c>
       <c r="K182" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="L182" t="s" s="2">
         <v>551</v>
       </c>
-      <c r="L182" t="s" s="2">
+      <c r="M182" t="s" s="2">
         <v>552</v>
-      </c>
-      <c r="M182" t="s" s="2">
-        <v>553</v>
       </c>
       <c r="N182" s="2"/>
       <c r="O182" s="2"/>
@@ -24790,7 +24788,7 @@
         <v>81</v>
       </c>
       <c r="AI182" t="s" s="2">
-        <v>209</v>
+        <v>79</v>
       </c>
       <c r="AJ182" t="s" s="2">
         <v>120</v>
@@ -24819,7 +24817,7 @@
         <v>661</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24937,7 +24935,7 @@
         <v>662</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -25026,7 +25024,7 @@
         <v>81</v>
       </c>
       <c r="AI184" t="s" s="2">
-        <v>209</v>
+        <v>79</v>
       </c>
       <c r="AJ184" t="s" s="2">
         <v>120</v>
@@ -25055,7 +25053,7 @@
         <v>663</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -25081,13 +25079,13 @@
         <v>138</v>
       </c>
       <c r="L185" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="M185" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="M185" t="s" s="2">
+      <c r="N185" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="N185" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="O185" s="2"/>
       <c r="P185" t="s" s="2">
@@ -25095,7 +25093,7 @@
       </c>
       <c r="Q185" s="2"/>
       <c r="R185" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="S185" t="s" s="2">
         <v>79</v>
@@ -25137,7 +25135,7 @@
         <v>79</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>91</v>
@@ -25175,7 +25173,7 @@
         <v>664</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -25201,10 +25199,10 @@
         <v>177</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>234</v>
+        <v>562</v>
       </c>
       <c r="N186" s="2"/>
       <c r="O186" s="2"/>
@@ -25231,7 +25229,7 @@
         <v>79</v>
       </c>
       <c r="X186" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="Y186" s="2"/>
       <c r="Z186" t="s" s="2">
@@ -25253,7 +25251,7 @@
         <v>79</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>80</v>
@@ -25262,7 +25260,7 @@
         <v>91</v>
       </c>
       <c r="AI186" t="s" s="2">
-        <v>209</v>
+        <v>79</v>
       </c>
       <c r="AJ186" t="s" s="2">
         <v>103</v>
@@ -25317,16 +25315,16 @@
         <v>155</v>
       </c>
       <c r="L187" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="M187" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="M187" t="s" s="2">
+      <c r="N187" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="N187" t="s" s="2">
+      <c r="O187" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="O187" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="P187" t="s" s="2">
         <v>79</v>
@@ -25375,7 +25373,7 @@
         <v>79</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>80</v>
@@ -25384,7 +25382,7 @@
         <v>81</v>
       </c>
       <c r="AI187" t="s" s="2">
-        <v>209</v>
+        <v>79</v>
       </c>
       <c r="AJ187" t="s" s="2">
         <v>103</v>
@@ -25396,10 +25394,10 @@
         <v>79</v>
       </c>
       <c r="AM187" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AN187" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="AN187" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="AO187" t="s" s="2">
         <v>79</v>
@@ -25439,16 +25437,16 @@
         <v>105</v>
       </c>
       <c r="L188" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="M188" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="M188" t="s" s="2">
+      <c r="N188" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="N188" t="s" s="2">
+      <c r="O188" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="O188" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="P188" t="s" s="2">
         <v>79</v>
@@ -25497,7 +25495,7 @@
         <v>79</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>80</v>
@@ -25506,7 +25504,7 @@
         <v>91</v>
       </c>
       <c r="AI188" t="s" s="2">
-        <v>209</v>
+        <v>79</v>
       </c>
       <c r="AJ188" t="s" s="2">
         <v>103</v>
@@ -25518,10 +25516,10 @@
         <v>79</v>
       </c>
       <c r="AM188" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="AN188" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="AN188" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="AO188" t="s" s="2">
         <v>79</v>
@@ -25628,7 +25626,7 @@
         <v>91</v>
       </c>
       <c r="AI189" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AJ189" t="s" s="2">
         <v>103</v>
@@ -26313,7 +26311,7 @@
         <v>79</v>
       </c>
       <c r="X195" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="Y195" t="s" s="2">
         <v>706</v>
@@ -26486,7 +26484,7 @@
         <v>720</v>
       </c>
       <c r="AO196" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AP196" t="s" s="2">
         <v>79</v>
@@ -26557,7 +26555,7 @@
         <v>79</v>
       </c>
       <c r="X197" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="Y197" t="s" s="2">
         <v>726</v>
@@ -26762,7 +26760,7 @@
         <v>92</v>
       </c>
       <c r="K199" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L199" t="s" s="2">
         <v>739</v>
@@ -26846,7 +26844,7 @@
         <v>742</v>
       </c>
       <c r="AO199" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AP199" t="s" s="2">
         <v>79</v>
@@ -27206,7 +27204,7 @@
         <v>79</v>
       </c>
       <c r="AM202" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AN202" t="s" s="2">
         <v>765</v>
@@ -27643,7 +27641,7 @@
       </c>
       <c r="Y206" s="2"/>
       <c r="Z206" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="AA206" t="s" s="2">
         <v>79</v>
@@ -27722,7 +27720,7 @@
         <v>92</v>
       </c>
       <c r="K207" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L207" t="s" s="2">
         <v>780</v>
@@ -28334,7 +28332,7 @@
         <v>115</v>
       </c>
       <c r="O212" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P212" t="s" s="2">
         <v>79</v>
@@ -28444,7 +28442,7 @@
         <v>79</v>
       </c>
       <c r="K213" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="L213" t="s" s="2">
         <v>805</v>
